--- a/IAG Solar Flux Atlas/Final data/Values NIR.xlsx
+++ b/IAG Solar Flux Atlas/Final data/Values NIR.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\clauw\Documents\Programming\Final-Project\IAG Solar Flux Atlas\Final data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4CDDEEC-4952-4777-BD61-8C8A547362FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13056" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>Emitted wavelength</t>
   </si>
@@ -34,17 +40,14 @@
     <t>Bisector slope</t>
   </si>
   <si>
-    <t>Blueshift</t>
-  </si>
-  <si>
     <t>Line Depth</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -107,13 +110,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -151,7 +162,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -185,6 +196,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -219,9 +231,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -394,11 +407,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H228"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G228"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -420,45 +433,39 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>8001.1458</v>
+        <v>8001.1458000000002</v>
       </c>
       <c r="B2">
-        <v>8001.1581</v>
+        <v>8001.1580999999996</v>
       </c>
       <c r="C2">
-        <v>0.4183500338082419</v>
+        <v>0.41835003380824187</v>
       </c>
       <c r="D2">
         <v>-172</v>
       </c>
       <c r="E2">
-        <v>5117100142.562213</v>
+        <v>5117100142.5622129</v>
       </c>
       <c r="F2">
-        <v>-16101437.46498079</v>
+        <v>-429.73111349777361</v>
       </c>
       <c r="G2">
-        <v>460.8648967691788</v>
-      </c>
-      <c r="H2">
-        <v>0.5816499661917581</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+        <v>0.58164996619175813</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>8030.5224</v>
+        <v>8030.5223999999998</v>
       </c>
       <c r="B3">
-        <v>8030.5316</v>
+        <v>8030.5316000000003</v>
       </c>
       <c r="C3">
-        <v>0.5793154851279907</v>
+        <v>0.57931548512799069</v>
       </c>
       <c r="D3">
         <v>-290</v>
@@ -467,50 +474,44 @@
         <v>5844466743.460619</v>
       </c>
       <c r="F3">
-        <v>5328526.35177646</v>
+        <v>142.7350759083258</v>
       </c>
       <c r="G3">
-        <v>343.4509582626749</v>
-      </c>
-      <c r="H3">
-        <v>0.4206845148720093</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+        <v>0.42068451487200931</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>8048.2606</v>
+        <v>8048.2605999999996</v>
       </c>
       <c r="B4">
-        <v>8048.2733</v>
+        <v>8048.2732999999998</v>
       </c>
       <c r="C4">
-        <v>0.4406432425179613</v>
+        <v>0.44064324251796128</v>
       </c>
       <c r="D4">
         <v>-160</v>
       </c>
       <c r="E4">
-        <v>5416007204.856009</v>
+        <v>5416007204.8560085</v>
       </c>
       <c r="F4">
-        <v>-11392783.10178046</v>
+        <v>-305.85236420707702</v>
       </c>
       <c r="G4">
-        <v>473.0667166225604</v>
-      </c>
-      <c r="H4">
-        <v>0.5593567574820386</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+        <v>0.55935675748203861</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>8074.3845</v>
+        <v>8074.3845000000001</v>
       </c>
       <c r="B5">
-        <v>8074.3861</v>
+        <v>8074.3860999999997</v>
       </c>
       <c r="C5">
-        <v>0.9145468547695467</v>
+        <v>0.91454685476954667</v>
       </c>
       <c r="D5">
         <v>-574</v>
@@ -519,44 +520,38 @@
         <v>1803377650.752327</v>
       </c>
       <c r="F5">
-        <v>-31939613.80773089</v>
+        <v>-860.23769740234877</v>
       </c>
       <c r="G5">
-        <v>59.40612971022731</v>
-      </c>
-      <c r="H5">
-        <v>0.08545314523045333</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+        <v>8.5453145230453331E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>8077.3715</v>
+        <v>8077.3715000000002</v>
       </c>
       <c r="B6">
-        <v>8077.377</v>
+        <v>8077.3770000000004</v>
       </c>
       <c r="C6">
-        <v>0.745143662825304</v>
+        <v>0.74514366282530398</v>
       </c>
       <c r="D6">
         <v>-429</v>
       </c>
       <c r="E6">
-        <v>5579761988.96913</v>
+        <v>5579761988.9691296</v>
       </c>
       <c r="F6">
-        <v>2675215.313045335</v>
+        <v>72.078940156794019</v>
       </c>
       <c r="G6">
-        <v>204.1330547768963</v>
-      </c>
-      <c r="H6">
-        <v>0.254856337174696</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
+        <v>0.25485633717469602</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>8099.1019</v>
+        <v>8099.1018999999997</v>
       </c>
       <c r="B7">
         <v>8099.1043</v>
@@ -568,27 +563,24 @@
         <v>-544</v>
       </c>
       <c r="E7">
-        <v>4119829383.082216</v>
+        <v>4119829383.0822158</v>
       </c>
       <c r="F7">
-        <v>-13747382.06991414</v>
+        <v>-371.39520446569918</v>
       </c>
       <c r="G7">
-        <v>88.83724495324149</v>
-      </c>
-      <c r="H7">
         <v>0.2398689216542147</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>8206.358399999999</v>
+        <v>8206.3583999999992</v>
       </c>
       <c r="B8">
-        <v>8206.364100000001</v>
+        <v>8206.3641000000007</v>
       </c>
       <c r="C8">
-        <v>0.9522209161427942</v>
+        <v>0.95222091614279425</v>
       </c>
       <c r="D8">
         <v>-425</v>
@@ -597,47 +589,41 @@
         <v>993230912.4523313</v>
       </c>
       <c r="F8">
-        <v>51777918.25531451</v>
+        <v>1417.3420251390969</v>
       </c>
       <c r="G8">
-        <v>208.2308531614801</v>
-      </c>
-      <c r="H8">
-        <v>0.04777908385720575</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
+        <v>4.7779083857205751E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>8209.999299999999</v>
+        <v>8209.9992999999995</v>
       </c>
       <c r="B9">
-        <v>8210.0075</v>
+        <v>8210.0074999999997</v>
       </c>
       <c r="C9">
-        <v>0.614162276447479</v>
+        <v>0.61416227644747901</v>
       </c>
       <c r="D9">
         <v>-334</v>
       </c>
       <c r="E9">
-        <v>6006150894.000401</v>
+        <v>6006150894.0004005</v>
       </c>
       <c r="F9">
-        <v>-3446801.119013046</v>
+        <v>-94.392845059849719</v>
       </c>
       <c r="G9">
-        <v>299.4273282917338</v>
-      </c>
-      <c r="H9">
-        <v>0.385837723552521</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
+        <v>0.38583772355252099</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>8218.063399999999</v>
+        <v>8218.0633999999991</v>
       </c>
       <c r="B10">
-        <v>8218.0645</v>
+        <v>8218.0645000000004</v>
       </c>
       <c r="C10">
         <v>0.9271666653719286</v>
@@ -646,105 +632,93 @@
         <v>-593</v>
       </c>
       <c r="E10">
-        <v>1099893807.644229</v>
+        <v>1099893807.6442289</v>
       </c>
       <c r="F10">
-        <v>44080479.64973152</v>
+        <v>1208.3566990615591</v>
       </c>
       <c r="G10">
-        <v>40.12766609656833</v>
-      </c>
-      <c r="H10">
-        <v>0.0728333346280714</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
+        <v>7.28333346280714E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>8222.638800000001</v>
+        <v>8222.6388000000006</v>
       </c>
       <c r="B11">
-        <v>8222.6536</v>
+        <v>8222.6535999999996</v>
       </c>
       <c r="C11">
-        <v>0.3744405567383206</v>
+        <v>0.37444055673832061</v>
       </c>
       <c r="D11">
         <v>-93</v>
       </c>
       <c r="E11">
-        <v>4826085771.36713</v>
+        <v>4826085771.3671303</v>
       </c>
       <c r="F11">
-        <v>-11719974.61371546</v>
+        <v>-321.45335507198138</v>
       </c>
       <c r="G11">
-        <v>539.5990856589589</v>
-      </c>
-      <c r="H11">
-        <v>0.6255594432616794</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
+        <v>0.62555944326167945</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>8241.393</v>
       </c>
       <c r="B12">
-        <v>8241.3999</v>
+        <v>8241.3999000000003</v>
       </c>
       <c r="C12">
-        <v>0.685846514621151</v>
+        <v>0.68584651462115098</v>
       </c>
       <c r="D12">
         <v>-382</v>
       </c>
       <c r="E12">
-        <v>6309069900.471977</v>
+        <v>6309069900.4719772</v>
       </c>
       <c r="F12">
-        <v>1365234.703235604</v>
+        <v>37.530781200381092</v>
       </c>
       <c r="G12">
-        <v>250.9973690310747</v>
-      </c>
-      <c r="H12">
-        <v>0.314153485378849</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
+        <v>0.31415348537884902</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>8250.398300000001</v>
+        <v>8250.3983000000007</v>
       </c>
       <c r="B13">
-        <v>8250.4058</v>
+        <v>8250.4058000000005</v>
       </c>
       <c r="C13">
-        <v>0.6358619068429034</v>
+        <v>0.63586190684290345</v>
       </c>
       <c r="D13">
         <v>-360</v>
       </c>
       <c r="E13">
-        <v>5847644154.387046</v>
+        <v>5847644154.3870459</v>
       </c>
       <c r="F13">
-        <v>-3126471.331867334</v>
+        <v>-86.041714931907947</v>
       </c>
       <c r="G13">
-        <v>272.525440993782</v>
-      </c>
-      <c r="H13">
-        <v>0.3641380931570966</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
+        <v>0.36413809315709661</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>8266.5506</v>
+        <v>8266.5506000000005</v>
       </c>
       <c r="B14">
-        <v>8266.552299999999</v>
+        <v>8266.5522999999994</v>
       </c>
       <c r="C14">
-        <v>0.8666956814007234</v>
+        <v>0.86669568140072339</v>
       </c>
       <c r="D14">
         <v>-571</v>
@@ -753,24 +727,21 @@
         <v>2095025263.279362</v>
       </c>
       <c r="F14">
-        <v>9853915.320588868</v>
+        <v>271.71432830848312</v>
       </c>
       <c r="G14">
-        <v>61.65173396973989</v>
-      </c>
-      <c r="H14">
-        <v>0.1333043185992766</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
+        <v>0.13330431859927661</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>8271.921899999999</v>
+        <v>8271.9218999999994</v>
       </c>
       <c r="B15">
-        <v>8271.926100000001</v>
+        <v>8271.9261000000006</v>
       </c>
       <c r="C15">
-        <v>0.8948161390212006</v>
+        <v>0.89481613902120061</v>
       </c>
       <c r="D15">
         <v>-481</v>
@@ -779,180 +750,159 @@
         <v>2025772519.612114</v>
       </c>
       <c r="F15">
-        <v>1166891.643314497</v>
+        <v>32.19707895455155</v>
       </c>
       <c r="G15">
-        <v>152.2171436604011</v>
-      </c>
-      <c r="H15">
-        <v>0.1051838609787994</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
+        <v>0.10518386097879941</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>8278.1669</v>
+        <v>8278.1669000000002</v>
       </c>
       <c r="B16">
-        <v>8278.172500000001</v>
+        <v>8278.1725000000006</v>
       </c>
       <c r="C16">
-        <v>0.7735236158321938</v>
+        <v>0.77352361583219376</v>
       </c>
       <c r="D16">
         <v>-430</v>
       </c>
       <c r="E16">
-        <v>3457408398.164316</v>
+        <v>3457408398.1643162</v>
       </c>
       <c r="F16">
-        <v>14469486.65127628</v>
+        <v>399.54609693921128</v>
       </c>
       <c r="G16">
-        <v>202.8030825017334</v>
-      </c>
-      <c r="H16">
-        <v>0.2264763841678062</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8">
+        <v>0.22647638416780619</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>8295.7942</v>
+        <v>8295.7942000000003</v>
       </c>
       <c r="B17">
-        <v>8295.802600000001</v>
+        <v>8295.8026000000009</v>
       </c>
       <c r="C17">
-        <v>0.6172502792396709</v>
+        <v>0.61725027923967091</v>
       </c>
       <c r="D17">
         <v>-329</v>
       </c>
       <c r="E17">
-        <v>6183104180.333494</v>
+        <v>6183104180.3334942</v>
       </c>
       <c r="F17">
-        <v>5590552.624832254</v>
+        <v>154.70075968528951</v>
       </c>
       <c r="G17">
-        <v>303.5582352532722</v>
-      </c>
-      <c r="H17">
-        <v>0.3827497207603291</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8">
+        <v>0.38274972076032909</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>8334.205599999999</v>
+        <v>8334.2055999999993</v>
       </c>
       <c r="B18">
         <v>8334.2181</v>
       </c>
       <c r="C18">
-        <v>0.4590771562006715</v>
+        <v>0.45907715620067152</v>
       </c>
       <c r="D18">
         <v>-183</v>
       </c>
       <c r="E18">
-        <v>5179614968.959443</v>
+        <v>5179614968.9594431</v>
       </c>
       <c r="F18">
-        <v>-2283296.745956765</v>
+        <v>-63.475556372482103</v>
       </c>
       <c r="G18">
-        <v>449.6416221193597</v>
-      </c>
-      <c r="H18">
-        <v>0.5409228437993285</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8">
+        <v>0.54092284379932853</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>8363.0934</v>
+        <v>8363.0933999999997</v>
       </c>
       <c r="B19">
-        <v>8363.099899999999</v>
+        <v>8363.0998999999993</v>
       </c>
       <c r="C19">
-        <v>0.6682151131312384</v>
+        <v>0.66821511313123838</v>
       </c>
       <c r="D19">
         <v>-400</v>
       </c>
       <c r="E19">
-        <v>5591980999.686174</v>
+        <v>5591980999.6861744</v>
       </c>
       <c r="F19">
-        <v>-5622224.307076626</v>
+        <v>-156.83924757136521</v>
       </c>
       <c r="G19">
-        <v>233.0060042921284</v>
-      </c>
-      <c r="H19">
-        <v>0.3317848868687616</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8">
+        <v>0.33178488686876162</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>8367.9326</v>
+        <v>8367.9326000000001</v>
       </c>
       <c r="B20">
-        <v>8367.942800000001</v>
+        <v>8367.9428000000007</v>
       </c>
       <c r="C20">
-        <v>0.5904912607306557</v>
+        <v>0.59049126073065572</v>
       </c>
       <c r="D20">
         <v>-268</v>
       </c>
       <c r="E20">
-        <v>6755273752.740248</v>
+        <v>6755273752.7402477</v>
       </c>
       <c r="F20">
-        <v>-1175526.398940946</v>
+        <v>-32.811824993368631</v>
       </c>
       <c r="G20">
-        <v>365.4287406505287</v>
-      </c>
-      <c r="H20">
-        <v>0.4095087392693443</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8">
+        <v>0.40950873926934428</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>8403.7088</v>
+        <v>8403.7088000000003</v>
       </c>
       <c r="B21">
-        <v>8403.716200000001</v>
+        <v>8403.7162000000008</v>
       </c>
       <c r="C21">
-        <v>0.7945286254189127</v>
+        <v>0.79452862541891267</v>
       </c>
       <c r="D21">
         <v>-369</v>
       </c>
       <c r="E21">
-        <v>4549819794.985278</v>
+        <v>4549819794.9852781</v>
       </c>
       <c r="F21">
-        <v>5581508.180526836</v>
+        <v>156.45960885755809</v>
       </c>
       <c r="G21">
-        <v>263.9863234175524</v>
-      </c>
-      <c r="H21">
         <v>0.2054713745810873</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>8426.4555</v>
       </c>
       <c r="B22">
-        <v>8426.459699999999</v>
+        <v>8426.4596999999994</v>
       </c>
       <c r="C22">
-        <v>0.7936664017315533</v>
+        <v>0.79366640173155334</v>
       </c>
       <c r="D22">
         <v>-484</v>
@@ -961,21 +911,18 @@
         <v>3741815257.22474</v>
       </c>
       <c r="F22">
-        <v>-5721946.471614324</v>
+        <v>-160.83043472899939</v>
       </c>
       <c r="G22">
-        <v>149.4256183281506</v>
-      </c>
-      <c r="H22">
-        <v>0.2063335982684467</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8">
+        <v>0.20633359826844669</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>8441.891100000001</v>
+        <v>8441.8911000000007</v>
       </c>
       <c r="B23">
-        <v>8441.9004</v>
+        <v>8441.9004000000004</v>
       </c>
       <c r="C23">
         <v>0.6026180756093239</v>
@@ -987,24 +934,21 @@
         <v>5824659385.77631</v>
       </c>
       <c r="F23">
-        <v>-6024250.427745188</v>
+        <v>-169.6377635213301</v>
       </c>
       <c r="G23">
-        <v>330.2660300174602</v>
-      </c>
-      <c r="H23">
         <v>0.3973819243906761</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>8470.7343</v>
+        <v>8470.7343000000001</v>
       </c>
       <c r="B24">
-        <v>8470.7484</v>
+        <v>8470.7484000000004</v>
       </c>
       <c r="C24">
-        <v>0.4173546843817695</v>
+        <v>0.41735468438176948</v>
       </c>
       <c r="D24">
         <v>-134</v>
@@ -1013,154 +957,136 @@
         <v>4844748931.975193</v>
       </c>
       <c r="F24">
-        <v>-24571688.03597509</v>
+        <v>-694.28226615372409</v>
       </c>
       <c r="G24">
-        <v>499.0209240425326</v>
-      </c>
-      <c r="H24">
-        <v>0.5826453156182305</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
+        <v>0.58264531561823052</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>8474.072099999999</v>
+        <v>8474.0720999999994</v>
       </c>
       <c r="B25">
-        <v>8474.0749</v>
+        <v>8474.0748999999996</v>
       </c>
       <c r="C25">
-        <v>0.7834289636366809</v>
+        <v>0.78342896363668091</v>
       </c>
       <c r="D25">
         <v>-534</v>
       </c>
       <c r="E25">
-        <v>3967389532.218083</v>
+        <v>3967389532.2180829</v>
       </c>
       <c r="F25">
-        <v>-10329654.59551664</v>
+        <v>-291.98288481806043</v>
       </c>
       <c r="G25">
-        <v>99.05732126728971</v>
-      </c>
-      <c r="H25">
-        <v>0.2165710363633191</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
+        <v>0.21657103636331909</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26">
-        <v>8516.4113</v>
+        <v>8516.4112999999998</v>
       </c>
       <c r="B26">
-        <v>8516.4246</v>
+        <v>8516.4246000000003</v>
       </c>
       <c r="C26">
-        <v>0.4359119002896</v>
+        <v>0.43591190028959997</v>
       </c>
       <c r="D26">
         <v>-165</v>
       </c>
       <c r="E26">
-        <v>5348343161.690667</v>
+        <v>5348343161.6906672</v>
       </c>
       <c r="F26">
-        <v>-24606886.72004183</v>
+        <v>-699.02590875710951</v>
       </c>
       <c r="G26">
-        <v>468.1830821665931</v>
-      </c>
-      <c r="H26">
-        <v>0.5640880997104001</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8">
+        <v>0.56408809971040008</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>8529.0116</v>
+        <v>8529.0115999999998</v>
       </c>
       <c r="B27">
-        <v>8529.018899999999</v>
+        <v>8529.0188999999991</v>
       </c>
       <c r="C27">
-        <v>0.6543778982904396</v>
+        <v>0.65437789829043957</v>
       </c>
       <c r="D27">
         <v>-376</v>
       </c>
       <c r="E27">
-        <v>5515088915.371831</v>
+        <v>5515088915.3718309</v>
       </c>
       <c r="F27">
-        <v>-5642554.795957162</v>
+        <v>-160.52924353088389</v>
       </c>
       <c r="G27">
-        <v>256.5930316024024</v>
-      </c>
-      <c r="H27">
-        <v>0.3456221017095604</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8">
+        <v>0.34562210170956043</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>8574.160099999999</v>
+        <v>8574.1600999999991</v>
       </c>
       <c r="B28">
-        <v>8574.1628</v>
+        <v>8574.1628000000001</v>
       </c>
       <c r="C28">
-        <v>0.8132657708772452</v>
+        <v>0.81326577087724516</v>
       </c>
       <c r="D28">
         <v>-539</v>
       </c>
       <c r="E28">
-        <v>3330338054.010527</v>
+        <v>3330338054.0105271</v>
       </c>
       <c r="F28">
-        <v>-3505383.614566269</v>
+        <v>-100.2551231216885</v>
       </c>
       <c r="G28">
-        <v>94.40453960430163</v>
-      </c>
-      <c r="H28">
-        <v>0.1867342291227548</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8">
+        <v>0.18673422912275481</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>8601.1924</v>
+        <v>8601.1923999999999</v>
       </c>
       <c r="B29">
-        <v>8601.199500000001</v>
+        <v>8601.1995000000006</v>
       </c>
       <c r="C29">
-        <v>0.6826620853355884</v>
+        <v>0.68266208533558836</v>
       </c>
       <c r="D29">
         <v>-386</v>
       </c>
       <c r="E29">
-        <v>5254130047.430035</v>
+        <v>5254130047.4300346</v>
       </c>
       <c r="F29">
-        <v>-1337839.926882251</v>
+        <v>-38.383314199917791</v>
       </c>
       <c r="G29">
-        <v>247.4687639794099</v>
-      </c>
-      <c r="H29">
-        <v>0.3173379146644116</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8">
+        <v>0.31733791466441158</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30">
-        <v>8612.9773</v>
+        <v>8612.9773000000005</v>
       </c>
       <c r="B30">
-        <v>8612.981900000001</v>
+        <v>8612.9819000000007</v>
       </c>
       <c r="C30">
-        <v>0.8416823847918976</v>
+        <v>0.84168238479189761</v>
       </c>
       <c r="D30">
         <v>-473</v>
@@ -1169,76 +1095,67 @@
         <v>3010050859.412271</v>
       </c>
       <c r="F30">
-        <v>-15125149.0152719</v>
+        <v>-434.542735238989</v>
       </c>
       <c r="G30">
-        <v>160.1124975524262</v>
-      </c>
-      <c r="H30">
-        <v>0.1583176152081024</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8">
+        <v>0.15831761520810239</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31">
-        <v>8614.169599999999</v>
+        <v>8614.1695999999993</v>
       </c>
       <c r="B31">
-        <v>8614.1813</v>
+        <v>8614.1813000000002</v>
       </c>
       <c r="C31">
-        <v>0.4861737235065751</v>
+        <v>0.48617372350657512</v>
       </c>
       <c r="D31">
         <v>-226</v>
       </c>
       <c r="E31">
-        <v>6313463175.955635</v>
+        <v>6313463175.9556351</v>
       </c>
       <c r="F31">
-        <v>-17290270.06038923</v>
+        <v>-496.81543698525849</v>
       </c>
       <c r="G31">
-        <v>407.1862897951532</v>
-      </c>
-      <c r="H31">
-        <v>0.5138262764934249</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8">
+        <v>0.51382627649342494</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32">
-        <v>8616.307199999999</v>
+        <v>8616.3071999999993</v>
       </c>
       <c r="B32">
-        <v>8616.310100000001</v>
+        <v>8616.3101000000006</v>
       </c>
       <c r="C32">
-        <v>0.8111433895891269</v>
+        <v>0.81114338958912691</v>
       </c>
       <c r="D32">
         <v>-532</v>
       </c>
       <c r="E32">
-        <v>3459253788.517984</v>
+        <v>3459253788.5179839</v>
       </c>
       <c r="F32">
-        <v>-455670.3888047609</v>
+        <v>-13.09638474403979</v>
       </c>
       <c r="G32">
-        <v>100.9014776574091</v>
-      </c>
-      <c r="H32">
-        <v>0.1888566104108731</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8">
+        <v>0.18885661041087309</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33">
-        <v>8618.6464</v>
+        <v>8618.6463999999996</v>
       </c>
       <c r="B33">
-        <v>8618.652599999999</v>
+        <v>8618.6525999999994</v>
       </c>
       <c r="C33">
-        <v>0.7409668908252277</v>
+        <v>0.74096689082522771</v>
       </c>
       <c r="D33">
         <v>-417</v>
@@ -1247,47 +1164,41 @@
         <v>4648542508.136076</v>
       </c>
       <c r="F33">
-        <v>-1023537.081946008</v>
+        <v>-29.425391790577919</v>
       </c>
       <c r="G33">
-        <v>215.6618514234176</v>
-      </c>
-      <c r="H33">
-        <v>0.2590331091747723</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8">
+        <v>0.25903310917477229</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34">
-        <v>8623.968999999999</v>
+        <v>8623.9689999999991</v>
       </c>
       <c r="B34">
-        <v>8623.9805</v>
+        <v>8623.9804999999997</v>
       </c>
       <c r="C34">
-        <v>0.5853643689054038</v>
+        <v>0.58536436890540378</v>
       </c>
       <c r="D34">
         <v>-233</v>
       </c>
       <c r="E34">
-        <v>6417998803.579285</v>
+        <v>6417998803.5792847</v>
       </c>
       <c r="F34">
-        <v>1445591.157539198</v>
+        <v>41.584601683310083</v>
       </c>
       <c r="G34">
-        <v>399.7710644547503</v>
-      </c>
-      <c r="H34">
-        <v>0.4146356310945962</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8">
+        <v>0.41463563109459622</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35">
-        <v>8677.1291</v>
+        <v>8677.1291000000001</v>
       </c>
       <c r="B35">
-        <v>8677.142</v>
+        <v>8677.1419999999998</v>
       </c>
       <c r="C35">
         <v>0.4644217265397822</v>
@@ -1296,128 +1207,113 @@
         <v>-187</v>
       </c>
       <c r="E35">
-        <v>5861011641.375013</v>
+        <v>5861011641.3750134</v>
       </c>
       <c r="F35">
-        <v>-18098913.08227985</v>
+        <v>-523.85186708265996</v>
       </c>
       <c r="G35">
-        <v>445.6915027526201</v>
-      </c>
-      <c r="H35">
         <v>0.5355782734602178</v>
       </c>
     </row>
-    <row r="36" spans="1:8">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36">
-        <v>8691.0119</v>
+        <v>8691.0118999999995</v>
       </c>
       <c r="B36">
-        <v>8691.029399999999</v>
+        <v>8691.0293999999994</v>
       </c>
       <c r="C36">
-        <v>0.3261076943862085</v>
+        <v>0.32610769438620851</v>
       </c>
       <c r="D36">
         <v>-29</v>
       </c>
       <c r="E36">
-        <v>3414520055.58295</v>
+        <v>3414520055.5829501</v>
       </c>
       <c r="F36">
-        <v>-29911501.57609661</v>
+        <v>-867.13902454478011</v>
       </c>
       <c r="G36">
-        <v>603.654450725946</v>
-      </c>
-      <c r="H36">
-        <v>0.6738923056137915</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8">
+        <v>0.67389230561379154</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37">
-        <v>8701.8433</v>
+        <v>8701.8433000000005</v>
       </c>
       <c r="B37">
-        <v>8701.8513</v>
+        <v>8701.8513000000003</v>
       </c>
       <c r="C37">
-        <v>0.6416226739786074</v>
+        <v>0.64162267397860739</v>
       </c>
       <c r="D37">
         <v>-357</v>
       </c>
       <c r="E37">
-        <v>5754445101.230829</v>
+        <v>5754445101.2308292</v>
       </c>
       <c r="F37">
-        <v>-7965836.275801811</v>
+        <v>-231.21836758205961</v>
       </c>
       <c r="G37">
-        <v>275.6128306725886</v>
-      </c>
-      <c r="H37">
-        <v>0.3583773260213926</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8">
+        <v>0.35837732602139261</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38">
-        <v>8712.783799999999</v>
+        <v>8712.7837999999992</v>
       </c>
       <c r="B38">
-        <v>8712.793</v>
+        <v>8712.7929999999997</v>
       </c>
       <c r="C38">
-        <v>0.6116963657344772</v>
+        <v>0.61169636573447717</v>
       </c>
       <c r="D38">
         <v>-316</v>
       </c>
       <c r="E38">
-        <v>5499155275.109694</v>
+        <v>5499155275.1096935</v>
       </c>
       <c r="F38">
-        <v>-15854570.56082867</v>
+        <v>-460.77740688324508</v>
       </c>
       <c r="G38">
-        <v>316.5567604195722</v>
-      </c>
-      <c r="H38">
-        <v>0.3883036342655228</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8">
+        <v>0.38830363426552278</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>8759.5926</v>
+        <v>8759.5925999999999</v>
       </c>
       <c r="B39">
-        <v>8759.6041</v>
+        <v>8759.6041000000005</v>
       </c>
       <c r="C39">
-        <v>0.5053187415174799</v>
+        <v>0.50531874151747991</v>
       </c>
       <c r="D39">
         <v>-239</v>
       </c>
       <c r="E39">
-        <v>6331792975.210806</v>
+        <v>6331792975.2108059</v>
       </c>
       <c r="F39">
-        <v>-13270211.61391177</v>
+        <v>-387.74090861581698</v>
       </c>
       <c r="G39">
-        <v>393.5814625569145</v>
-      </c>
-      <c r="H39">
-        <v>0.4946812584825201</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8">
+        <v>0.49468125848252009</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>8766.3732</v>
       </c>
       <c r="B40">
-        <v>8766.3848</v>
+        <v>8766.3847999999998</v>
       </c>
       <c r="C40">
         <v>0.5315223443354018</v>
@@ -1426,79 +1322,70 @@
         <v>-236</v>
       </c>
       <c r="E40">
-        <v>5629802771.25153</v>
+        <v>5629802771.2515297</v>
       </c>
       <c r="F40">
-        <v>-10540975.20575436</v>
+        <v>-308.23405444343069</v>
       </c>
       <c r="G40">
-        <v>396.6968361292472</v>
-      </c>
-      <c r="H40">
         <v>0.4684776556645982</v>
       </c>
     </row>
-    <row r="41" spans="1:8">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>8786.852800000001</v>
+        <v>8786.8528000000006</v>
       </c>
       <c r="B41">
-        <v>8786.8568</v>
+        <v>8786.8567999999996</v>
       </c>
       <c r="C41">
-        <v>0.8256651749099981</v>
+        <v>0.82566517490999813</v>
       </c>
       <c r="D41">
         <v>-497</v>
       </c>
       <c r="E41">
-        <v>3345795179.650215</v>
+        <v>3345795179.6502151</v>
       </c>
       <c r="F41">
-        <v>-5065719.389124373</v>
+        <v>-148.47521901708191</v>
       </c>
       <c r="G41">
-        <v>136.4731900171342</v>
-      </c>
-      <c r="H41">
-        <v>0.1743348250900019</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8">
+        <v>0.17433482509000189</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>8795.758599999999</v>
+        <v>8795.7585999999992</v>
       </c>
       <c r="B42">
-        <v>8795.7708</v>
+        <v>8795.7708000000002</v>
       </c>
       <c r="C42">
-        <v>0.5133936622199436</v>
+        <v>0.51339366221994365</v>
       </c>
       <c r="D42">
         <v>-217</v>
       </c>
       <c r="E42">
-        <v>5444408168.317199</v>
+        <v>5444408168.3171988</v>
       </c>
       <c r="F42">
-        <v>-12487659.64144151</v>
+        <v>-366.38210569836849</v>
       </c>
       <c r="G42">
-        <v>415.8217789121333</v>
-      </c>
-      <c r="H42">
-        <v>0.4866063377800564</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8">
+        <v>0.48660633778005641</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>8798.8992</v>
+        <v>8798.8991999999998</v>
       </c>
       <c r="B43">
-        <v>8798.9043</v>
+        <v>8798.9043000000001</v>
       </c>
       <c r="C43">
-        <v>0.8410872462308429</v>
+        <v>0.84108724623084286</v>
       </c>
       <c r="D43">
         <v>-459</v>
@@ -1507,76 +1394,67 @@
         <v>2928443171.073019</v>
       </c>
       <c r="F43">
-        <v>-3298549.743579921</v>
+        <v>-96.81238719670948</v>
       </c>
       <c r="G43">
-        <v>173.7650928179621</v>
-      </c>
-      <c r="H43">
-        <v>0.1589127537691571</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8">
+        <v>0.15891275376915709</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44">
-        <v>8807.0437</v>
+        <v>8807.0437000000002</v>
       </c>
       <c r="B44">
-        <v>8807.0524</v>
+        <v>8807.0524000000005</v>
       </c>
       <c r="C44">
-        <v>0.6328672581267445</v>
+        <v>0.63286725812674449</v>
       </c>
       <c r="D44">
         <v>-337</v>
       </c>
       <c r="E44">
-        <v>6864598746.393819</v>
+        <v>6864598746.3938189</v>
       </c>
       <c r="F44">
-        <v>-2718568.167022568</v>
+        <v>-79.863824659457265</v>
       </c>
       <c r="G44">
-        <v>296.1486820457557</v>
-      </c>
-      <c r="H44">
-        <v>0.3671327418732555</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8">
+        <v>0.36713274187325551</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45">
-        <v>8810.5898</v>
+        <v>8810.5897999999997</v>
       </c>
       <c r="B45">
-        <v>8810.5924</v>
+        <v>8810.5923999999995</v>
       </c>
       <c r="C45">
-        <v>0.7822332203216668</v>
+        <v>0.78223322032166676</v>
       </c>
       <c r="D45">
         <v>-545</v>
       </c>
       <c r="E45">
-        <v>3628584148.864644</v>
+        <v>3628584148.8646441</v>
       </c>
       <c r="F45">
-        <v>-2034679.436817387</v>
+        <v>-59.797138667376181</v>
       </c>
       <c r="G45">
-        <v>88.46858254313892</v>
-      </c>
-      <c r="H45">
-        <v>0.2177667796783332</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8">
+        <v>0.21776677967833319</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46">
-        <v>8826.644200000001</v>
+        <v>8826.6442000000006</v>
       </c>
       <c r="B46">
-        <v>8826.660599999999</v>
+        <v>8826.6605999999992</v>
       </c>
       <c r="C46">
-        <v>0.3730135604979997</v>
+        <v>0.37301356049799972</v>
       </c>
       <c r="D46">
         <v>-76</v>
@@ -1585,50 +1463,44 @@
         <v>3917674448.773458</v>
       </c>
       <c r="F46">
-        <v>-37875759.50427946</v>
+        <v>-1115.1597219683861</v>
       </c>
       <c r="G46">
-        <v>557.0176161666278</v>
-      </c>
-      <c r="H46">
-        <v>0.6269864395020003</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8">
+        <v>0.62698643950200028</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47">
-        <v>8849.169900000001</v>
+        <v>8849.1699000000008</v>
       </c>
       <c r="B47">
-        <v>8849.175499999999</v>
+        <v>8849.1754999999994</v>
       </c>
       <c r="C47">
-        <v>0.7241950020435733</v>
+        <v>0.72419500204357334</v>
       </c>
       <c r="D47">
         <v>-443</v>
       </c>
       <c r="E47">
-        <v>4831790660.989968</v>
+        <v>4831790660.9899683</v>
       </c>
       <c r="F47">
-        <v>353689.0491620245</v>
+        <v>10.440077410029049</v>
       </c>
       <c r="G47">
-        <v>189.7169772045815</v>
-      </c>
-      <c r="H47">
-        <v>0.2758049979564267</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8">
+        <v>0.27580499795642671</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>8869.3676</v>
+        <v>8869.3675999999996</v>
       </c>
       <c r="B48">
-        <v>8869.3814</v>
+        <v>8869.3814000000002</v>
       </c>
       <c r="C48">
-        <v>0.4783560402304017</v>
+        <v>0.47835604023040168</v>
       </c>
       <c r="D48">
         <v>-167</v>
@@ -1637,73 +1509,64 @@
         <v>5084090748.316783</v>
       </c>
       <c r="F48">
-        <v>-11841721.59125557</v>
+        <v>-350.33818370927969</v>
       </c>
       <c r="G48">
-        <v>466.4521877039886</v>
-      </c>
-      <c r="H48">
-        <v>0.5216439597695983</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8">
+        <v>0.52164395976959832</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>8878.4612</v>
+        <v>8878.4611999999997</v>
       </c>
       <c r="B49">
-        <v>8878.4656</v>
+        <v>8878.4655999999995</v>
       </c>
       <c r="C49">
-        <v>0.7963134715662138</v>
+        <v>0.79631347156621379</v>
       </c>
       <c r="D49">
         <v>-484</v>
       </c>
       <c r="E49">
-        <v>3849391923.317758</v>
+        <v>3849391923.3177581</v>
       </c>
       <c r="F49">
-        <v>3304540.890761679</v>
+        <v>97.865212547878443</v>
       </c>
       <c r="G49">
-        <v>148.571558231961</v>
-      </c>
-      <c r="H49">
-        <v>0.2036865284337862</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8">
+        <v>0.20368652843378621</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50">
-        <v>8945.519200000001</v>
+        <v>8945.5192000000006</v>
       </c>
       <c r="B50">
-        <v>8945.5265</v>
+        <v>8945.5264999999999</v>
       </c>
       <c r="C50">
-        <v>0.7360877098634784</v>
+        <v>0.73608770986347838</v>
       </c>
       <c r="D50">
         <v>-388</v>
       </c>
       <c r="E50">
-        <v>5169436779.741717</v>
+        <v>5169436779.7417173</v>
       </c>
       <c r="F50">
-        <v>-9123216.851114867</v>
+        <v>-272.22825634557688</v>
       </c>
       <c r="G50">
-        <v>244.6459388368232</v>
-      </c>
-      <c r="H50">
-        <v>0.2639122901365216</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8">
+        <v>0.26391229013652162</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51">
-        <v>8947.6459</v>
+        <v>8947.6458999999995</v>
       </c>
       <c r="B51">
-        <v>8947.655500000001</v>
+        <v>8947.6555000000008</v>
       </c>
       <c r="C51">
         <v>0.616342692242554</v>
@@ -1712,24 +1575,21 @@
         <v>-311</v>
       </c>
       <c r="E51">
-        <v>5657051164.879713</v>
+        <v>5657051164.8797131</v>
       </c>
       <c r="F51">
-        <v>-8411117.936088672</v>
+        <v>-251.0396230914937</v>
       </c>
       <c r="G51">
-        <v>321.6496975043341</v>
-      </c>
-      <c r="H51">
         <v>0.383657307757446</v>
       </c>
     </row>
-    <row r="52" spans="1:8">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52">
-        <v>8952.6461</v>
+        <v>8952.6460999999999</v>
       </c>
       <c r="B52">
-        <v>8952.651099999999</v>
+        <v>8952.6510999999991</v>
       </c>
       <c r="C52">
         <v>0.9135065051155129</v>
@@ -1738,154 +1598,136 @@
         <v>-466</v>
       </c>
       <c r="E52">
-        <v>1574533395.565287</v>
+        <v>1574533395.5652871</v>
       </c>
       <c r="F52">
-        <v>27547422.9966399</v>
+        <v>822.64399991354492</v>
       </c>
       <c r="G52">
-        <v>167.432318108946</v>
-      </c>
-      <c r="H52">
-        <v>0.0864934948844871</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8">
+        <v>8.6493494884487099E-2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53">
-        <v>8977.8647</v>
+        <v>8977.8647000000001</v>
       </c>
       <c r="B53">
-        <v>8977.8765</v>
+        <v>8977.8765000000003</v>
       </c>
       <c r="C53">
-        <v>0.552310307651117</v>
+        <v>0.55231030765111699</v>
       </c>
       <c r="D53">
         <v>-239</v>
       </c>
       <c r="E53">
-        <v>5817634611.925939</v>
+        <v>5817634611.9259386</v>
       </c>
       <c r="F53">
-        <v>-5349926.402478306</v>
+        <v>-160.21409893353459</v>
       </c>
       <c r="G53">
-        <v>394.0303315714157</v>
-      </c>
-      <c r="H53">
-        <v>0.447689692348883</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8">
+        <v>0.44768969234888301</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54">
-        <v>9013.0681</v>
+        <v>9013.0681000000004</v>
       </c>
       <c r="B54">
-        <v>9013.0761</v>
+        <v>9013.0761000000002</v>
       </c>
       <c r="C54">
-        <v>0.6856895596539552</v>
+        <v>0.68568955965395517</v>
       </c>
       <c r="D54">
         <v>-367</v>
       </c>
       <c r="E54">
-        <v>5275280114.195532</v>
+        <v>5275280114.1955318</v>
       </c>
       <c r="F54">
-        <v>5555925.27035531</v>
+        <v>167.03548048438731</v>
       </c>
       <c r="G54">
-        <v>266.0958107997598</v>
-      </c>
-      <c r="H54">
-        <v>0.3143104403460448</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8">
+        <v>0.31431044034604477</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55">
-        <v>9016.451999999999</v>
+        <v>9016.4519999999993</v>
       </c>
       <c r="B55">
-        <v>9016.4593</v>
+        <v>9016.4593000000004</v>
       </c>
       <c r="C55">
-        <v>0.7616192846685423</v>
+        <v>0.76161928466854234</v>
       </c>
       <c r="D55">
         <v>-390</v>
       </c>
       <c r="E55">
-        <v>3564589075.296008</v>
+        <v>3564589075.2960081</v>
       </c>
       <c r="F55">
-        <v>-2473658.258210362</v>
+        <v>-74.396931650837658</v>
       </c>
       <c r="G55">
-        <v>242.7212991886152</v>
-      </c>
-      <c r="H55">
-        <v>0.2383807153314577</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8">
+        <v>0.23838071533145769</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56">
-        <v>9022.222900000001</v>
+        <v>9022.2229000000007</v>
       </c>
       <c r="B56">
-        <v>9022.2281</v>
+        <v>9022.2281000000003</v>
       </c>
       <c r="C56">
-        <v>0.8299457500636225</v>
+        <v>0.82994575006362248</v>
       </c>
       <c r="D56">
         <v>-460</v>
       </c>
       <c r="E56">
-        <v>2426840321.957208</v>
+        <v>2426840321.9572082</v>
       </c>
       <c r="F56">
-        <v>2804027.32638745</v>
+        <v>84.386959919120855</v>
       </c>
       <c r="G56">
-        <v>172.786773144405</v>
-      </c>
-      <c r="H56">
-        <v>0.1700542499363775</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8">
+        <v>0.17005424993637749</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57">
-        <v>9039.2359</v>
+        <v>9039.2358999999997</v>
       </c>
       <c r="B57">
-        <v>9039.2395</v>
+        <v>9039.2394999999997</v>
       </c>
       <c r="C57">
-        <v>0.9633207531010954</v>
+        <v>0.96332075310109544</v>
       </c>
       <c r="D57">
         <v>-514</v>
       </c>
       <c r="E57">
-        <v>708347112.0032234</v>
+        <v>708347112.00322342</v>
       </c>
       <c r="F57">
-        <v>280251383.7111135</v>
+        <v>8450.0437218175557</v>
       </c>
       <c r="G57">
-        <v>119.3964690044329</v>
-      </c>
-      <c r="H57">
-        <v>0.03667924689890456</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8">
+        <v>3.6679246898904561E-2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58">
-        <v>9086.6788</v>
+        <v>9086.6787999999997</v>
       </c>
       <c r="B58">
-        <v>9086.6859</v>
+        <v>9086.6859000000004</v>
       </c>
       <c r="C58">
         <v>0.9214180886223734</v>
@@ -1897,180 +1739,159 @@
         <v>1279210288.999572</v>
       </c>
       <c r="F58">
-        <v>-33675890.58087179</v>
+        <v>-1020.713603512836</v>
       </c>
       <c r="G58">
-        <v>234.2469123185328</v>
-      </c>
-      <c r="H58">
-        <v>0.0785819113776266</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8">
+        <v>7.8581911377626601E-2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59">
-        <v>9106.136200000001</v>
+        <v>9106.1362000000008</v>
       </c>
       <c r="B59">
-        <v>9106.1379</v>
+        <v>9106.1378999999997</v>
       </c>
       <c r="C59">
-        <v>0.8275217245181556</v>
+        <v>0.82752172451815564</v>
       </c>
       <c r="D59">
         <v>-577</v>
       </c>
       <c r="E59">
-        <v>3286725858.309904</v>
+        <v>3286725858.3099041</v>
       </c>
       <c r="F59">
-        <v>30755696.20035777</v>
+        <v>934.19832066276956</v>
       </c>
       <c r="G59">
-        <v>55.96744516247381</v>
-      </c>
-      <c r="H59">
-        <v>0.1724782754818444</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8">
+        <v>0.17247827548184441</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60">
-        <v>9212.5533</v>
+        <v>9212.5532999999996</v>
       </c>
       <c r="B60">
-        <v>9212.561400000001</v>
+        <v>9212.5614000000005</v>
       </c>
       <c r="C60">
-        <v>0.6208887864800217</v>
+        <v>0.62088878648002166</v>
       </c>
       <c r="D60">
         <v>-369</v>
       </c>
       <c r="E60">
-        <v>6902957415.375627</v>
+        <v>6902957415.3756266</v>
       </c>
       <c r="F60">
-        <v>-3388898.256628235</v>
+        <v>-104.1401557458146</v>
       </c>
       <c r="G60">
-        <v>263.5880446175102</v>
-      </c>
-      <c r="H60">
-        <v>0.3791112135199783</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8">
+        <v>0.37911121351997829</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61">
-        <v>9786.674000000001</v>
+        <v>9786.6740000000009</v>
       </c>
       <c r="B61">
-        <v>9786.6787</v>
+        <v>9786.6787000000004</v>
       </c>
       <c r="C61">
-        <v>0.8331108631341189</v>
+        <v>0.83311086313411886</v>
       </c>
       <c r="D61">
         <v>-489</v>
       </c>
       <c r="E61">
-        <v>2857069670.986645</v>
+        <v>2857069670.9866452</v>
       </c>
       <c r="F61">
-        <v>-12219435.72174382</v>
+        <v>-398.90160046657797</v>
       </c>
       <c r="G61">
-        <v>143.9737905132135</v>
-      </c>
-      <c r="H61">
-        <v>0.1668891368658811</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8">
+        <v>0.16688913686588111</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62">
-        <v>9802.9961</v>
+        <v>9802.9961000000003</v>
       </c>
       <c r="B62">
-        <v>9803.002399999999</v>
+        <v>9803.0023999999994</v>
       </c>
       <c r="C62">
-        <v>0.6882651419806538</v>
+        <v>0.68826514198065381</v>
       </c>
       <c r="D62">
         <v>-440</v>
       </c>
       <c r="E62">
-        <v>4526353725.876134</v>
+        <v>4526353725.8761339</v>
       </c>
       <c r="F62">
-        <v>-11320430.1155893</v>
+        <v>-370.17009811552418</v>
       </c>
       <c r="G62">
-        <v>192.6648205920298</v>
-      </c>
-      <c r="H62">
-        <v>0.3117348580193462</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8">
+        <v>0.31173485801934619</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63">
-        <v>9803.4871</v>
+        <v>9803.4871000000003</v>
       </c>
       <c r="B63">
-        <v>9803.493399999999</v>
+        <v>9803.4933999999994</v>
       </c>
       <c r="C63">
-        <v>0.8303061357734076</v>
+        <v>0.83030613577340762</v>
       </c>
       <c r="D63">
         <v>-440</v>
       </c>
       <c r="E63">
-        <v>2262869858.583948</v>
+        <v>2262869858.5839481</v>
       </c>
       <c r="F63">
-        <v>27825076.64952466</v>
+        <v>909.90599666156072</v>
       </c>
       <c r="G63">
-        <v>192.6551711296614</v>
-      </c>
-      <c r="H63">
-        <v>0.1696938642265924</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8">
+        <v>0.16969386422659241</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64">
-        <v>9836.8809</v>
+        <v>9836.8809000000001</v>
       </c>
       <c r="B64">
-        <v>9836.8873</v>
+        <v>9836.8873000000003</v>
       </c>
       <c r="C64">
-        <v>0.835785413826749</v>
+        <v>0.83578541382674898</v>
       </c>
       <c r="D64">
         <v>-438</v>
       </c>
       <c r="E64">
-        <v>3066727224.254328</v>
+        <v>3066727224.2543278</v>
       </c>
       <c r="F64">
-        <v>17413758.93661031</v>
+        <v>571.38590233915579</v>
       </c>
       <c r="G64">
-        <v>195.0487914372474</v>
-      </c>
-      <c r="H64">
-        <v>0.164214586173251</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8">
+        <v>0.16421458617325099</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65">
-        <v>9864.4409</v>
+        <v>9864.4408999999996</v>
       </c>
       <c r="B65">
-        <v>9864.446599999999</v>
+        <v>9864.4465999999993</v>
       </c>
       <c r="C65">
-        <v>0.6562490974027125</v>
+        <v>0.65624909740271253</v>
       </c>
       <c r="D65">
         <v>-460</v>
@@ -2079,24 +1900,21 @@
         <v>5205384999.769969</v>
       </c>
       <c r="F65">
-        <v>-7116142.235643431</v>
+        <v>-234.1513377281467</v>
       </c>
       <c r="G65">
-        <v>173.2299911944204</v>
-      </c>
-      <c r="H65">
-        <v>0.3437509025972875</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8">
+        <v>0.34375090259728752</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66">
-        <v>9891.7477</v>
+        <v>9891.7476999999999</v>
       </c>
       <c r="B66">
         <v>9891.759</v>
       </c>
       <c r="C66">
-        <v>0.6402522765218723</v>
+        <v>0.64025227652187233</v>
       </c>
       <c r="D66">
         <v>-291</v>
@@ -2105,125 +1923,110 @@
         <v>5137780700.566062</v>
       </c>
       <c r="F66">
-        <v>435441.0116057455</v>
+        <v>14.36753137238775</v>
       </c>
       <c r="G66">
-        <v>342.4728246447154</v>
-      </c>
-      <c r="H66">
-        <v>0.3597477234781277</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8">
+        <v>0.35974772347812772</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>9946.9321</v>
       </c>
       <c r="B67">
-        <v>9946.9388</v>
+        <v>9946.9387999999999</v>
       </c>
       <c r="C67">
-        <v>0.8423492616663094</v>
+        <v>0.84234926166630941</v>
       </c>
       <c r="D67">
         <v>-431</v>
       </c>
       <c r="E67">
-        <v>2835712381.330403</v>
+        <v>2835712381.3304029</v>
       </c>
       <c r="F67">
-        <v>31805407.15847062</v>
+        <v>1055.2848481411399</v>
       </c>
       <c r="G67">
-        <v>201.9325605790433</v>
-      </c>
-      <c r="H67">
-        <v>0.1576507383336906</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8">
+        <v>0.15765073833369059</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68">
-        <v>9956.2017</v>
+        <v>9956.2016999999996</v>
       </c>
       <c r="B68">
-        <v>9956.206700000001</v>
+        <v>9956.2067000000006</v>
       </c>
       <c r="C68">
-        <v>0.9562685504021226</v>
+        <v>0.95626855040212255</v>
       </c>
       <c r="D68">
         <v>-482</v>
       </c>
       <c r="E68">
-        <v>768246039.314449</v>
+        <v>768246039.31444895</v>
       </c>
       <c r="F68">
-        <v>-295986301.1654549</v>
+        <v>-9829.8029724674398</v>
       </c>
       <c r="G68">
-        <v>150.5556371518064</v>
-      </c>
-      <c r="H68">
-        <v>0.04373144959787745</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8">
+        <v>4.3731449597877448E-2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69">
-        <v>9972.9673</v>
+        <v>9972.9673000000003</v>
       </c>
       <c r="B69">
-        <v>9972.976500000001</v>
+        <v>9972.9765000000007</v>
       </c>
       <c r="C69">
-        <v>0.9749602462522619</v>
+        <v>0.97496024625226185</v>
       </c>
       <c r="D69">
         <v>-356</v>
       </c>
       <c r="E69">
-        <v>553699268.9256721</v>
+        <v>553699268.92567205</v>
       </c>
       <c r="F69">
-        <v>539745448.725239</v>
+        <v>17955.317195200299</v>
       </c>
       <c r="G69">
-        <v>276.5566686855374</v>
-      </c>
-      <c r="H69">
-        <v>0.02503975374773815</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8">
+        <v>2.5039753747738151E-2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70">
-        <v>9980.3766</v>
+        <v>9980.3765999999996</v>
       </c>
       <c r="B70">
-        <v>9980.3815</v>
+        <v>9980.3814999999995</v>
       </c>
       <c r="C70">
-        <v>0.9410441733776592</v>
+        <v>0.94104417337765922</v>
       </c>
       <c r="D70">
         <v>-486</v>
       </c>
       <c r="E70">
-        <v>1089231620.260306</v>
+        <v>1089231620.2603059</v>
       </c>
       <c r="F70">
-        <v>-134335757.5925896</v>
+        <v>-4472.1675748946491</v>
       </c>
       <c r="G70">
-        <v>147.1871356378689</v>
-      </c>
-      <c r="H70">
-        <v>0.05895582662234078</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8">
+        <v>5.8955826622340779E-2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71">
-        <v>9983.2003</v>
+        <v>9983.2003000000004</v>
       </c>
       <c r="B71">
-        <v>9983.205</v>
+        <v>9983.2049999999999</v>
       </c>
       <c r="C71">
         <v>0.8916722270177988</v>
@@ -2232,71 +2035,62 @@
         <v>-492</v>
       </c>
       <c r="E71">
-        <v>2053302813.942164</v>
+        <v>2053302813.9421639</v>
       </c>
       <c r="F71">
-        <v>-37986573.71771846</v>
+        <v>-1264.9676219392929</v>
       </c>
       <c r="G71">
-        <v>141.1395654545929</v>
-      </c>
-      <c r="H71">
         <v>0.1083277729822012</v>
       </c>
     </row>
-    <row r="72" spans="1:8">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72">
-        <v>9998.803099999999</v>
+        <v>9998.8030999999992</v>
       </c>
       <c r="B72">
-        <v>9998.808999999999</v>
+        <v>9998.8089999999993</v>
       </c>
       <c r="C72">
-        <v>0.9777339280413752</v>
+        <v>0.97773392804137516</v>
       </c>
       <c r="D72">
         <v>-456</v>
       </c>
       <c r="E72">
-        <v>359451929.7712027</v>
+        <v>359451929.77120268</v>
       </c>
       <c r="F72">
-        <v>633055458.3982732</v>
+        <v>21113.942149044251</v>
       </c>
       <c r="G72">
-        <v>176.8987232039831</v>
-      </c>
-      <c r="H72">
-        <v>0.02226607195862484</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8">
+        <v>2.2266071958624841E-2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73">
-        <v>10035.6094</v>
+        <v>10035.609399999999</v>
       </c>
       <c r="B73">
-        <v>10035.6164</v>
+        <v>10035.616400000001</v>
       </c>
       <c r="C73">
-        <v>0.9425659457279744</v>
+        <v>0.94256594572797436</v>
       </c>
       <c r="D73">
         <v>-424</v>
       </c>
       <c r="E73">
-        <v>1092414854.350568</v>
+        <v>1092414854.3505681</v>
       </c>
       <c r="F73">
-        <v>156677110.1056063</v>
+        <v>5244.7996396241178</v>
       </c>
       <c r="G73">
-        <v>209.110092138397</v>
-      </c>
-      <c r="H73">
-        <v>0.05743405427202564</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8">
+        <v>5.7434054272025643E-2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>10084.1584</v>
       </c>
@@ -2304,51 +2098,45 @@
         <v>10084.1685</v>
       </c>
       <c r="C74">
-        <v>0.9566354357463792</v>
+        <v>0.95663543574637921</v>
       </c>
       <c r="D74">
         <v>-333</v>
       </c>
       <c r="E74">
-        <v>1039916995.203525</v>
+        <v>1039916995.2035249</v>
       </c>
       <c r="F74">
-        <v>95784039.45845836</v>
+        <v>3221.9035794080678</v>
       </c>
       <c r="G74">
-        <v>300.2634136864436</v>
-      </c>
-      <c r="H74">
-        <v>0.04336456425362079</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8">
+        <v>4.3364564253620792E-2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75">
-        <v>10116.7892</v>
+        <v>10116.789199999999</v>
       </c>
       <c r="B75">
         <v>10116.797</v>
       </c>
       <c r="C75">
-        <v>0.8921159934809142</v>
+        <v>0.89211599348091419</v>
       </c>
       <c r="D75">
         <v>-402</v>
       </c>
       <c r="E75">
-        <v>2487722571.704799</v>
+        <v>2487722571.7047992</v>
       </c>
       <c r="F75">
-        <v>62683098.96488434</v>
+        <v>2115.3040066092831</v>
       </c>
       <c r="G75">
-        <v>231.1386673049972</v>
-      </c>
-      <c r="H75">
-        <v>0.1078840065190858</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8">
+        <v>0.10788400651908581</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>10139.8807</v>
       </c>
@@ -2356,33 +2144,30 @@
         <v>10139.8825</v>
       </c>
       <c r="C76">
-        <v>0.9455875591861581</v>
+        <v>0.94558755918615811</v>
       </c>
       <c r="D76">
         <v>-580</v>
       </c>
       <c r="E76">
-        <v>1164347933.249144</v>
+        <v>1164347933.2491441</v>
       </c>
       <c r="F76">
-        <v>166611754.3473985</v>
+        <v>5635.3105861038221</v>
       </c>
       <c r="G76">
-        <v>53.21822221639219</v>
-      </c>
-      <c r="H76">
-        <v>0.05441244081384189</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8">
+        <v>5.4412440813841889E-2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>10145.6242</v>
       </c>
       <c r="B77">
-        <v>10145.6287</v>
+        <v>10145.628699999999</v>
       </c>
       <c r="C77">
-        <v>0.9165798275178256</v>
+        <v>0.91657982751782563</v>
       </c>
       <c r="D77">
         <v>-500</v>
@@ -2391,24 +2176,21 @@
         <v>1427904249.565825</v>
       </c>
       <c r="F77">
-        <v>-22663026.0553909</v>
+        <v>-766.96608417154266</v>
       </c>
       <c r="G77">
-        <v>132.9702376056558</v>
-      </c>
-      <c r="H77">
-        <v>0.08342017248217437</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8">
+        <v>8.3420172482174371E-2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>10148.3444</v>
       </c>
       <c r="B78">
-        <v>10148.3569</v>
+        <v>10148.356900000001</v>
       </c>
       <c r="C78">
-        <v>0.578729376228426</v>
+        <v>0.57872937622842602</v>
       </c>
       <c r="D78">
         <v>-264</v>
@@ -2417,42 +2199,36 @@
         <v>4861451483.351841</v>
       </c>
       <c r="F78">
-        <v>-28409543.72762407</v>
+        <v>-961.69927368248023</v>
       </c>
       <c r="G78">
-        <v>369.2627661837664</v>
-      </c>
-      <c r="H78">
-        <v>0.421270623771574</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8">
+        <v>0.42127062377157398</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79">
-        <v>10157.949</v>
+        <v>10157.949000000001</v>
       </c>
       <c r="B79">
         <v>10157.9565</v>
       </c>
       <c r="C79">
-        <v>0.8922904980039206</v>
+        <v>0.89229049800392057</v>
       </c>
       <c r="D79">
         <v>-412</v>
       </c>
       <c r="E79">
-        <v>2369787863.916452</v>
+        <v>2369787863.9164519</v>
       </c>
       <c r="F79">
-        <v>45429471.48641107</v>
+        <v>1539.3002154075341</v>
       </c>
       <c r="G79">
-        <v>221.3481712655098</v>
-      </c>
-      <c r="H79">
         <v>0.1077095019960794</v>
       </c>
     </row>
-    <row r="80" spans="1:8">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>10170.2562</v>
       </c>
@@ -2460,77 +2236,68 @@
         <v>10170.2631</v>
       </c>
       <c r="C80">
-        <v>0.8727068181001285</v>
+        <v>0.87270681810012851</v>
       </c>
       <c r="D80">
         <v>-430</v>
       </c>
       <c r="E80">
-        <v>2893465557.268535</v>
+        <v>2893465557.2685351</v>
       </c>
       <c r="F80">
-        <v>52285354.05180201</v>
+        <v>1773.746446228068</v>
       </c>
       <c r="G80">
-        <v>203.3938889715005</v>
-      </c>
-      <c r="H80">
-        <v>0.1272931818998715</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8">
+        <v>0.12729318189987149</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>10219.1142</v>
       </c>
       <c r="B81">
-        <v>10219.1292</v>
+        <v>10219.129199999999</v>
       </c>
       <c r="C81">
-        <v>0.5526297645050298</v>
+        <v>0.55262976450502976</v>
       </c>
       <c r="D81">
         <v>-193</v>
       </c>
       <c r="E81">
-        <v>4898282972.106872</v>
+        <v>4898282972.1068716</v>
       </c>
       <c r="F81">
-        <v>-7300468.186603961</v>
+        <v>-248.85358396639711</v>
       </c>
       <c r="G81">
-        <v>440.04664022485</v>
-      </c>
-      <c r="H81">
-        <v>0.4473702354949702</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8">
+        <v>0.44737023549497018</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82">
-        <v>10221.2115</v>
+        <v>10221.211499999999</v>
       </c>
       <c r="B82">
-        <v>10221.2182</v>
+        <v>10221.218199999999</v>
       </c>
       <c r="C82">
-        <v>0.7701527816600178</v>
+        <v>0.77015278166001777</v>
       </c>
       <c r="D82">
         <v>-436</v>
       </c>
       <c r="E82">
-        <v>4769684636.022537</v>
+        <v>4769684636.0225372</v>
       </c>
       <c r="F82">
-        <v>3783279.059394291</v>
+        <v>128.98830422731919</v>
       </c>
       <c r="G82">
-        <v>196.5138348174656</v>
-      </c>
-      <c r="H82">
         <v>0.2298472183399822</v>
       </c>
     </row>
-    <row r="83" spans="1:8">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>10268.0337</v>
       </c>
@@ -2538,7 +2305,7 @@
         <v>10268.0393</v>
       </c>
       <c r="C83">
-        <v>0.947788576701416</v>
+        <v>0.94778857670141603</v>
       </c>
       <c r="D83">
         <v>-469</v>
@@ -2547,21 +2314,18 @@
         <v>1175894603.604178</v>
       </c>
       <c r="F83">
-        <v>101648915.6019635</v>
+        <v>3481.5254098331729</v>
       </c>
       <c r="G83">
-        <v>163.5013882968728</v>
-      </c>
-      <c r="H83">
-        <v>0.05221142329858397</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8">
+        <v>5.221142329858397E-2</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>10310.2796</v>
       </c>
       <c r="B84">
-        <v>10310.2815</v>
+        <v>10310.281499999999</v>
       </c>
       <c r="C84">
         <v>0.9618218832931974</v>
@@ -2570,19 +2334,16 @@
         <v>-578</v>
       </c>
       <c r="E84">
-        <v>651237286.9919277</v>
+        <v>651237286.99192774</v>
       </c>
       <c r="F84">
-        <v>406184614.3090176</v>
+        <v>13969.25640635996</v>
       </c>
       <c r="G84">
-        <v>55.24638439732712</v>
-      </c>
-      <c r="H84">
-        <v>0.0381781167068026</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8">
+        <v>3.8178116706802601E-2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>10335.161</v>
       </c>
@@ -2590,103 +2351,91 @@
         <v>10335.1693</v>
       </c>
       <c r="C85">
-        <v>0.9324216936338562</v>
+        <v>0.93242169363385619</v>
       </c>
       <c r="D85">
         <v>-392</v>
       </c>
       <c r="E85">
-        <v>1483377073.555127</v>
+        <v>1483377073.5551269</v>
       </c>
       <c r="F85">
-        <v>87995685.52016665</v>
+        <v>3033.599689557504</v>
       </c>
       <c r="G85">
-        <v>240.7584556362024</v>
-      </c>
-      <c r="H85">
-        <v>0.06757830636614381</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8">
+        <v>6.7578306366143814E-2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86">
-        <v>10343.7208</v>
+        <v>10343.720799999999</v>
       </c>
       <c r="B86">
         <v>10343.7289</v>
       </c>
       <c r="C86">
-        <v>0.7276842221210741</v>
+        <v>0.72768422212107409</v>
       </c>
       <c r="D86">
         <v>-398</v>
       </c>
       <c r="E86">
-        <v>5741618897.409628</v>
+        <v>5741618897.4096279</v>
       </c>
       <c r="F86">
-        <v>3332097.627462617</v>
+        <v>114.9672501994914</v>
       </c>
       <c r="G86">
-        <v>234.7626117048913</v>
-      </c>
-      <c r="H86">
-        <v>0.2723157778789259</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8">
+        <v>0.27231577787892591</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87">
-        <v>10348.0194</v>
+        <v>10348.019399999999</v>
       </c>
       <c r="B87">
         <v>10348.0221</v>
       </c>
       <c r="C87">
-        <v>0.9541308464388411</v>
+        <v>0.95413084643884105</v>
       </c>
       <c r="D87">
         <v>-555</v>
       </c>
       <c r="E87">
-        <v>816452194.0869088</v>
+        <v>816452194.08690882</v>
       </c>
       <c r="F87">
-        <v>24187923.80759507</v>
+        <v>834.90149079771027</v>
       </c>
       <c r="G87">
-        <v>78.22169691553601</v>
-      </c>
-      <c r="H87">
-        <v>0.04586915356115895</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8">
+        <v>4.5869153561158948E-2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88">
-        <v>10350.8021</v>
+        <v>10350.802100000001</v>
       </c>
       <c r="B88">
         <v>10350.8094</v>
       </c>
       <c r="C88">
-        <v>0.8204667728020646</v>
+        <v>0.82046677280206459</v>
       </c>
       <c r="D88">
         <v>-422</v>
       </c>
       <c r="E88">
-        <v>3023016423.668905</v>
+        <v>3023016423.6689048</v>
       </c>
       <c r="F88">
-        <v>977415.4649770735</v>
+        <v>33.746816881530968</v>
       </c>
       <c r="G88">
-        <v>211.4314352049752</v>
-      </c>
-      <c r="H88">
-        <v>0.1795332271979354</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8">
+        <v>0.17953322719793541</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>10365.544</v>
       </c>
@@ -2694,25 +2443,22 @@
         <v>10365.5494</v>
       </c>
       <c r="C89">
-        <v>0.9334676050653554</v>
+        <v>0.93346760506535542</v>
       </c>
       <c r="D89">
         <v>-477</v>
       </c>
       <c r="E89">
-        <v>1167710602.469932</v>
+        <v>1167710602.4699321</v>
       </c>
       <c r="F89">
-        <v>101261740.0364153</v>
+        <v>3501.2007162549121</v>
       </c>
       <c r="G89">
-        <v>156.1789013206684</v>
-      </c>
-      <c r="H89">
-        <v>0.06653239493464458</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8">
+        <v>6.6532394934644579E-2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>10381.8464</v>
       </c>
@@ -2720,25 +2466,22 @@
         <v>10381.8516</v>
       </c>
       <c r="C90">
-        <v>0.8817066134008689</v>
+        <v>0.88170661340086887</v>
       </c>
       <c r="D90">
         <v>-483</v>
       </c>
       <c r="E90">
-        <v>2620537720.623078</v>
+        <v>2620537720.6230779</v>
       </c>
       <c r="F90">
-        <v>8616107.045082089</v>
+        <v>298.37690150216099</v>
       </c>
       <c r="G90">
-        <v>150.158336158803</v>
-      </c>
-      <c r="H90">
-        <v>0.1182933865991311</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8">
+        <v>0.11829338659913111</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>10391.5915</v>
       </c>
@@ -2746,7 +2489,7 @@
         <v>10391.5985</v>
       </c>
       <c r="C91">
-        <v>0.9516161949802773</v>
+        <v>0.95161619498027727</v>
       </c>
       <c r="D91">
         <v>-431</v>
@@ -2755,18 +2498,15 @@
         <v>912103665.3756156</v>
       </c>
       <c r="F91">
-        <v>155365542.5129987</v>
+        <v>5385.3801036240984</v>
       </c>
       <c r="G91">
-        <v>201.9466609972183</v>
-      </c>
-      <c r="H91">
-        <v>0.04838380501972273</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8">
+        <v>4.8383805019722732E-2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92">
-        <v>10398.6467</v>
+        <v>10398.646699999999</v>
       </c>
       <c r="B92">
         <v>10398.6551</v>
@@ -2778,45 +2518,39 @@
         <v>-391</v>
       </c>
       <c r="E92">
-        <v>6334397162.849628</v>
+        <v>6334397162.8496284</v>
       </c>
       <c r="F92">
-        <v>-5619379.032977202</v>
+        <v>-194.9147914858533</v>
       </c>
       <c r="G92">
-        <v>242.1715747933119</v>
-      </c>
-      <c r="H92">
         <v>0.3273813461267876</v>
       </c>
     </row>
-    <row r="93" spans="1:8">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>10425.8871</v>
       </c>
       <c r="B93">
-        <v>10425.8954</v>
+        <v>10425.895399999999</v>
       </c>
       <c r="C93">
-        <v>0.8627504163799893</v>
+        <v>0.86275041637998928</v>
       </c>
       <c r="D93">
         <v>-394</v>
       </c>
       <c r="E93">
-        <v>2907342842.092541</v>
+        <v>2907342842.0925412</v>
       </c>
       <c r="F93">
-        <v>23491007.64812877</v>
+        <v>816.94779853331238</v>
       </c>
       <c r="G93">
-        <v>238.6633748817404</v>
-      </c>
-      <c r="H93">
-        <v>0.1372495836200107</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8">
+        <v>0.13724958362001069</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>10426.6023</v>
       </c>
@@ -2824,7 +2558,7 @@
         <v>10426.6096</v>
       </c>
       <c r="C94">
-        <v>0.8242190357561556</v>
+        <v>0.82421903575615563</v>
       </c>
       <c r="D94">
         <v>-423</v>
@@ -2833,70 +2567,61 @@
         <v>3650308171.970758</v>
       </c>
       <c r="F94">
-        <v>-4861517.001753004</v>
+        <v>-169.08077067449469</v>
       </c>
       <c r="G94">
-        <v>209.894352961243</v>
-      </c>
-      <c r="H94">
         <v>0.1757809642438444</v>
       </c>
     </row>
-    <row r="95" spans="1:8">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>10472.5234</v>
       </c>
       <c r="B95">
-        <v>10472.5387</v>
+        <v>10472.538699999999</v>
       </c>
       <c r="C95">
-        <v>0.6155480611350826</v>
+        <v>0.61554806113508265</v>
       </c>
       <c r="D95">
         <v>-195</v>
       </c>
       <c r="E95">
-        <v>5367784831.088258</v>
+        <v>5367784831.0882578</v>
       </c>
       <c r="F95">
-        <v>-7306275.050283175</v>
+        <v>-255.22739540343929</v>
       </c>
       <c r="G95">
-        <v>437.9865704075818</v>
-      </c>
-      <c r="H95">
-        <v>0.3844519388649174</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8">
+        <v>0.38445193886491741</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96">
-        <v>10535.122</v>
+        <v>10535.121999999999</v>
       </c>
       <c r="B96">
-        <v>10535.1339</v>
+        <v>10535.133900000001</v>
       </c>
       <c r="C96">
-        <v>0.6914731478923564</v>
+        <v>0.69147314789235637</v>
       </c>
       <c r="D96">
         <v>-294</v>
       </c>
       <c r="E96">
-        <v>5502191211.121552</v>
+        <v>5502191211.1215525</v>
       </c>
       <c r="F96">
-        <v>3667309.38911736</v>
+        <v>128.87447444417899</v>
       </c>
       <c r="G96">
-        <v>338.6320776117072</v>
-      </c>
-      <c r="H96">
-        <v>0.3085268521076436</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8">
+        <v>0.30852685210764358</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97">
-        <v>10558.5438</v>
+        <v>10558.543799999999</v>
       </c>
       <c r="B97">
         <v>10558.5496</v>
@@ -2908,45 +2633,39 @@
         <v>-468</v>
       </c>
       <c r="E97">
-        <v>1109103792.656712</v>
+        <v>1109103792.6567121</v>
       </c>
       <c r="F97">
-        <v>25102531.12714076</v>
+        <v>884.09935913551112</v>
       </c>
       <c r="G97">
-        <v>164.6814456252225</v>
-      </c>
-      <c r="H97">
-        <v>0.0670847560112463</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8">
+        <v>6.7084756011246305E-2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98">
-        <v>10580.039</v>
+        <v>10580.039000000001</v>
       </c>
       <c r="B98">
         <v>10580.0488</v>
       </c>
       <c r="C98">
-        <v>0.8966317783067991</v>
+        <v>0.89663177830679908</v>
       </c>
       <c r="D98">
         <v>-355</v>
       </c>
       <c r="E98">
-        <v>2276211567.059862</v>
+        <v>2276211567.0598621</v>
       </c>
       <c r="F98">
-        <v>23994375.32402267</v>
+        <v>846.79135541720564</v>
       </c>
       <c r="G98">
-        <v>277.6895329283418</v>
-      </c>
-      <c r="H98">
         <v>0.1033682216932009</v>
       </c>
     </row>
-    <row r="99" spans="1:8">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>10619.6322</v>
       </c>
@@ -2954,7 +2673,7 @@
         <v>10619.6384</v>
       </c>
       <c r="C99">
-        <v>0.9075142607948093</v>
+        <v>0.90751426079480935</v>
       </c>
       <c r="D99">
         <v>-458</v>
@@ -2963,50 +2682,44 @@
         <v>2230216978.745636</v>
       </c>
       <c r="F99">
-        <v>28263552.39839941</v>
+        <v>1001.188316653564</v>
       </c>
       <c r="G99">
-        <v>175.0261407137777</v>
-      </c>
-      <c r="H99">
-        <v>0.09248573920519065</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8">
+        <v>9.2485739205190654E-2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100">
-        <v>10755.9531</v>
+        <v>10755.953100000001</v>
       </c>
       <c r="B100">
         <v>10755.9622</v>
       </c>
       <c r="C100">
-        <v>0.7951715445423577</v>
+        <v>0.79517154454235772</v>
       </c>
       <c r="D100">
         <v>-379</v>
       </c>
       <c r="E100">
-        <v>4012371034.929343</v>
+        <v>4012371034.9293432</v>
       </c>
       <c r="F100">
-        <v>9957776.974086111</v>
+        <v>357.26540101719502</v>
       </c>
       <c r="G100">
-        <v>253.6373431923298</v>
-      </c>
-      <c r="H100">
-        <v>0.2048284554576423</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8">
+        <v>0.20482845545764231</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>10783.6477</v>
       </c>
       <c r="B101">
-        <v>10783.6583</v>
+        <v>10783.658299999999</v>
       </c>
       <c r="C101">
-        <v>0.940933297218545</v>
+        <v>0.94093329721854502</v>
       </c>
       <c r="D101">
         <v>-338</v>
@@ -3015,50 +2728,44 @@
         <v>1423530335.532048</v>
       </c>
       <c r="F101">
-        <v>48341681.80190385</v>
+        <v>1738.870222676047</v>
       </c>
       <c r="G101">
-        <v>294.6869318163317</v>
-      </c>
-      <c r="H101">
-        <v>0.05906670278145498</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8">
+        <v>5.9066702781454983E-2</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102">
-        <v>10786.0053</v>
+        <v>10786.005300000001</v>
       </c>
       <c r="B102">
         <v>10786.0128</v>
       </c>
       <c r="C102">
-        <v>0.7509901897148473</v>
+        <v>0.75099018971484732</v>
       </c>
       <c r="D102">
         <v>-425</v>
       </c>
       <c r="E102">
-        <v>5131435504.372919</v>
+        <v>5131435504.3729191</v>
       </c>
       <c r="F102">
-        <v>8438671.782919452</v>
+        <v>303.60877812866141</v>
       </c>
       <c r="G102">
-        <v>208.4593297016262</v>
-      </c>
-      <c r="H102">
-        <v>0.2490098102851527</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8">
+        <v>0.24900981028515271</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103">
-        <v>10821.2401</v>
+        <v>10821.240100000001</v>
       </c>
       <c r="B103">
-        <v>10821.2494</v>
+        <v>10821.249400000001</v>
       </c>
       <c r="C103">
-        <v>0.8187263313830657</v>
+        <v>0.81872633138306572</v>
       </c>
       <c r="D103">
         <v>-375</v>
@@ -3067,47 +2774,41 @@
         <v>3567627233.572556</v>
       </c>
       <c r="F103">
-        <v>13690480.77423065</v>
+        <v>494.16889221360918</v>
       </c>
       <c r="G103">
-        <v>257.6479066640685</v>
-      </c>
-      <c r="H103">
-        <v>0.1812736686169343</v>
-      </c>
-    </row>
-    <row r="104" spans="1:8">
+        <v>0.18127366861693431</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104">
-        <v>10887.2463</v>
+        <v>10887.246300000001</v>
       </c>
       <c r="B104">
         <v>10887.2564</v>
       </c>
       <c r="C104">
-        <v>0.7992821301989513</v>
+        <v>0.79928213019895133</v>
       </c>
       <c r="D104">
         <v>-355</v>
       </c>
       <c r="E104">
-        <v>3740177205.343518</v>
+        <v>3740177205.3435178</v>
       </c>
       <c r="F104">
-        <v>5682019.626809872</v>
+        <v>206.34810148196391</v>
       </c>
       <c r="G104">
-        <v>278.1147539102653</v>
-      </c>
-      <c r="H104">
-        <v>0.2007178698010487</v>
-      </c>
-    </row>
-    <row r="105" spans="1:8">
+        <v>0.20071786980104869</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>10899.2871</v>
       </c>
       <c r="B105">
-        <v>10899.2954</v>
+        <v>10899.295400000001</v>
       </c>
       <c r="C105">
         <v>0.7771657279956552</v>
@@ -3116,27 +2817,24 @@
         <v>-405</v>
       </c>
       <c r="E105">
-        <v>4551789703.786042</v>
+        <v>4551789703.7860422</v>
       </c>
       <c r="F105">
-        <v>-7373565.200082134</v>
+        <v>-268.07433983831328</v>
       </c>
       <c r="G105">
-        <v>228.2972618982217</v>
-      </c>
-      <c r="H105">
         <v>0.2228342720043448</v>
       </c>
     </row>
-    <row r="106" spans="1:8">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106">
-        <v>11122.8432</v>
+        <v>11122.843199999999</v>
       </c>
       <c r="B106">
         <v>11122.8541</v>
       </c>
       <c r="C106">
-        <v>0.5788332976528966</v>
+        <v>0.57883329765289659</v>
       </c>
       <c r="D106">
         <v>-339</v>
@@ -3145,24 +2843,21 @@
         <v>5920332872.86448</v>
       </c>
       <c r="F106">
-        <v>-8343150.216613088</v>
+        <v>-309.54628816503038</v>
       </c>
       <c r="G106">
-        <v>293.786195995636</v>
-      </c>
-      <c r="H106">
-        <v>0.4211667023471034</v>
-      </c>
-    </row>
-    <row r="107" spans="1:8">
+        <v>0.42116670234710341</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107">
-        <v>11672.8365</v>
+        <v>11672.836499999999</v>
       </c>
       <c r="B107">
         <v>11672.8441</v>
       </c>
       <c r="C107">
-        <v>0.7174500684803052</v>
+        <v>0.71745006848030524</v>
       </c>
       <c r="D107">
         <v>-438</v>
@@ -3171,42 +2866,36 @@
         <v>5053048059.109766</v>
       </c>
       <c r="F107">
-        <v>29709112.09872661</v>
+        <v>1156.766371613857</v>
       </c>
       <c r="G107">
-        <v>195.1901477600028</v>
-      </c>
-      <c r="H107">
-        <v>0.2825499315196948</v>
-      </c>
-    </row>
-    <row r="108" spans="1:8">
+        <v>0.28254993151969482</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>11887.3385</v>
       </c>
       <c r="B108">
-        <v>11887.3563</v>
+        <v>11887.356299999999</v>
       </c>
       <c r="C108">
-        <v>0.4844950352663978</v>
+        <v>0.48449503526639781</v>
       </c>
       <c r="D108">
         <v>-184</v>
       </c>
       <c r="E108">
-        <v>4078361117.601238</v>
+        <v>4078361117.6012378</v>
       </c>
       <c r="F108">
-        <v>-33204587.71600025</v>
+        <v>-1316.626734401364</v>
       </c>
       <c r="G108">
-        <v>448.9066877308219</v>
-      </c>
-      <c r="H108">
         <v>0.5155049647336023</v>
       </c>
     </row>
-    <row r="109" spans="1:8">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>11893.7446</v>
       </c>
@@ -3214,25 +2903,22 @@
         <v>11893.751</v>
       </c>
       <c r="C109">
-        <v>0.7331483007404824</v>
+        <v>0.73314830074048243</v>
       </c>
       <c r="D109">
         <v>-472</v>
       </c>
       <c r="E109">
-        <v>3234104353.83377</v>
+        <v>3234104353.8337698</v>
       </c>
       <c r="F109">
-        <v>-7962682.93565054</v>
+        <v>-315.90577281492699</v>
       </c>
       <c r="G109">
-        <v>161.3177175190825</v>
-      </c>
-      <c r="H109">
-        <v>0.2668516992595176</v>
-      </c>
-    </row>
-    <row r="110" spans="1:8">
+        <v>0.26685169925951763</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>12056.3824</v>
       </c>
@@ -3240,30 +2926,27 @@
         <v>12056.391</v>
       </c>
       <c r="C110">
-        <v>0.8219597008949441</v>
+        <v>0.82195970089494408</v>
       </c>
       <c r="D110">
         <v>-419</v>
       </c>
       <c r="E110">
-        <v>3292310950.058791</v>
+        <v>3292310950.0587912</v>
       </c>
       <c r="F110">
-        <v>-8322813.517383904</v>
+        <v>-334.70853354711687</v>
       </c>
       <c r="G110">
-        <v>213.8464966395116</v>
-      </c>
-      <c r="H110">
-        <v>0.1780402991050559</v>
-      </c>
-    </row>
-    <row r="111" spans="1:8">
+        <v>0.17804029910505589</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>12134.4953</v>
       </c>
       <c r="B111">
-        <v>12134.4932</v>
+        <v>12134.493200000001</v>
       </c>
       <c r="C111">
         <v>0.9696413045972998</v>
@@ -3272,19 +2955,16 @@
         <v>-685</v>
       </c>
       <c r="E111">
-        <v>484919102.1449975</v>
+        <v>484919102.14499748</v>
       </c>
       <c r="F111">
-        <v>-37658692.86906283</v>
+        <v>-1524.2850190064869</v>
       </c>
       <c r="G111">
-        <v>-51.88218762412625</v>
-      </c>
-      <c r="H111">
-        <v>0.0303586954027002</v>
-      </c>
-    </row>
-    <row r="112" spans="1:8">
+        <v>3.0358695402700201E-2</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>12216.6754</v>
       </c>
@@ -3292,51 +2972,45 @@
         <v>12216.6782</v>
       </c>
       <c r="C112">
-        <v>0.8802837580998081</v>
+        <v>0.88028375809980808</v>
       </c>
       <c r="D112">
         <v>-564</v>
       </c>
       <c r="E112">
-        <v>1956128998.876171</v>
+        <v>1956128998.8761711</v>
       </c>
       <c r="F112">
-        <v>63107876.30689377</v>
+        <v>2571.6744906462109</v>
       </c>
       <c r="G112">
-        <v>68.71090987194373</v>
-      </c>
-      <c r="H112">
-        <v>0.1197162419001919</v>
-      </c>
-    </row>
-    <row r="113" spans="1:8">
+        <v>0.11971624190019189</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113">
-        <v>12230.459</v>
+        <v>12230.459000000001</v>
       </c>
       <c r="B113">
-        <v>12230.4677</v>
+        <v>12230.467699999999</v>
       </c>
       <c r="C113">
-        <v>0.7707975248510693</v>
+        <v>0.77079752485106934</v>
       </c>
       <c r="D113">
         <v>-420</v>
       </c>
       <c r="E113">
-        <v>3958370237.736347</v>
+        <v>3958370237.7363472</v>
       </c>
       <c r="F113">
-        <v>7461850.332053294</v>
+        <v>304.41699593527488</v>
       </c>
       <c r="G113">
-        <v>213.2540066162134</v>
-      </c>
-      <c r="H113">
-        <v>0.2292024751489307</v>
-      </c>
-    </row>
-    <row r="114" spans="1:8">
+        <v>0.22920247514893069</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>12343.864</v>
       </c>
@@ -3344,85 +3018,76 @@
         <v>12343.8663</v>
       </c>
       <c r="C114">
-        <v>0.9508750247068429</v>
+        <v>0.95087502470684293</v>
       </c>
       <c r="D114">
         <v>-577</v>
       </c>
       <c r="E114">
-        <v>885320110.7129227</v>
+        <v>885320110.71292269</v>
       </c>
       <c r="F114">
-        <v>-18408945.50113069</v>
+        <v>-757.98291760209543</v>
       </c>
       <c r="G114">
-        <v>55.85954716125617</v>
-      </c>
-      <c r="H114">
-        <v>0.04912497529315707</v>
-      </c>
-    </row>
-    <row r="115" spans="1:8">
+        <v>4.9124975293157069E-2</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115">
-        <v>12346.2918</v>
+        <v>12346.291800000001</v>
       </c>
       <c r="B115">
-        <v>12346.3034</v>
+        <v>12346.303400000001</v>
       </c>
       <c r="C115">
-        <v>0.8201837553729874</v>
+        <v>0.82018375537298738</v>
       </c>
       <c r="D115">
         <v>-351</v>
       </c>
       <c r="E115">
-        <v>2893479150.314776</v>
+        <v>2893479150.3147759</v>
       </c>
       <c r="F115">
-        <v>25835291.56025861</v>
+        <v>1063.9705553580411</v>
       </c>
       <c r="G115">
-        <v>281.6710125485241</v>
-      </c>
-      <c r="H115">
-        <v>0.1798162446270126</v>
-      </c>
-    </row>
-    <row r="116" spans="1:8">
+        <v>0.17981624462701259</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116">
-        <v>12560.4345</v>
+        <v>12560.434499999999</v>
       </c>
       <c r="B116">
-        <v>12560.4438</v>
+        <v>12560.443799999999</v>
       </c>
       <c r="C116">
-        <v>0.8253168036778873</v>
+        <v>0.82531680367788729</v>
       </c>
       <c r="D116">
         <v>-411</v>
       </c>
       <c r="E116">
-        <v>3698188201.947296</v>
+        <v>3698188201.9472961</v>
       </c>
       <c r="F116">
-        <v>7148187.431506136</v>
+        <v>299.48854318843189</v>
       </c>
       <c r="G116">
-        <v>221.9724054358576</v>
-      </c>
-      <c r="H116">
-        <v>0.1746831963221127</v>
-      </c>
-    </row>
-    <row r="117" spans="1:8">
+        <v>0.17468319632211271</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117">
-        <v>12619.3777</v>
+        <v>12619.377699999999</v>
       </c>
       <c r="B117">
-        <v>12619.3872</v>
+        <v>12619.387199999999</v>
       </c>
       <c r="C117">
-        <v>0.8312967932890556</v>
+        <v>0.83129679328905559</v>
       </c>
       <c r="D117">
         <v>-407</v>
@@ -3431,102 +3096,90 @@
         <v>2922384018.712894</v>
       </c>
       <c r="F117">
-        <v>-8848614.204445509</v>
+        <v>-372.4713075647748</v>
       </c>
       <c r="G117">
-        <v>225.6869093191555</v>
-      </c>
-      <c r="H117">
-        <v>0.1687032067109444</v>
-      </c>
-    </row>
-    <row r="118" spans="1:8">
+        <v>0.16870320671094441</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>12642.1643</v>
       </c>
       <c r="B118">
-        <v>12642.1791</v>
+        <v>12642.179099999999</v>
       </c>
       <c r="C118">
-        <v>0.6177090004850468</v>
+        <v>0.61770900048504684</v>
       </c>
       <c r="D118">
         <v>-282</v>
       </c>
       <c r="E118">
-        <v>4279152310.849101</v>
+        <v>4279152310.8491011</v>
       </c>
       <c r="F118">
-        <v>-4111393.746382472</v>
+        <v>-173.3765300139311</v>
       </c>
       <c r="G118">
-        <v>350.9627206966982</v>
-      </c>
-      <c r="H118">
-        <v>0.3822909995149532</v>
-      </c>
-    </row>
-    <row r="119" spans="1:8">
+        <v>0.38229099951495321</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>12810.6535</v>
       </c>
       <c r="B119">
-        <v>12810.6678</v>
+        <v>12810.667799999999</v>
       </c>
       <c r="C119">
-        <v>0.7946096144510806</v>
+        <v>0.79460961445108058</v>
       </c>
       <c r="D119">
         <v>-298</v>
       </c>
       <c r="E119">
-        <v>3337081972.08334</v>
+        <v>3337081972.0833402</v>
       </c>
       <c r="F119">
-        <v>12799969.90510492</v>
+        <v>546.96560213098053</v>
       </c>
       <c r="G119">
-        <v>334.645859331857</v>
-      </c>
-      <c r="H119">
-        <v>0.2053903855489194</v>
-      </c>
-    </row>
-    <row r="120" spans="1:8">
+        <v>0.20539038554891939</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>12828.3694</v>
       </c>
       <c r="B120">
-        <v>12828.3795</v>
+        <v>12828.379499999999</v>
       </c>
       <c r="C120">
-        <v>0.8446822807130892</v>
+        <v>0.84468228071308915</v>
       </c>
       <c r="D120">
         <v>-397</v>
       </c>
       <c r="E120">
-        <v>2273626482.28181</v>
+        <v>2273626482.2818098</v>
       </c>
       <c r="F120">
-        <v>4101617.602997416</v>
+        <v>175.5117774681683</v>
       </c>
       <c r="G120">
-        <v>236.03185496702</v>
-      </c>
-      <c r="H120">
-        <v>0.1553177192869108</v>
-      </c>
-    </row>
-    <row r="121" spans="1:8">
+        <v>0.15531771928691079</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>12844.0867</v>
       </c>
       <c r="B121">
-        <v>12844.1002</v>
+        <v>12844.100200000001</v>
       </c>
       <c r="C121">
-        <v>0.8833913014290545</v>
+        <v>0.88339130142905453</v>
       </c>
       <c r="D121">
         <v>-318</v>
@@ -3535,16 +3188,13 @@
         <v>1663237571.869143</v>
       </c>
       <c r="F121">
-        <v>24495923.06465667</v>
+        <v>1049.486342761636</v>
       </c>
       <c r="G121">
-        <v>315.1020603992357</v>
-      </c>
-      <c r="H121">
         <v>0.1166086985709455</v>
       </c>
     </row>
-    <row r="122" spans="1:8">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>12883.2924</v>
       </c>
@@ -3552,33 +3202,30 @@
         <v>12883.304</v>
       </c>
       <c r="C122">
-        <v>0.6898292624548639</v>
+        <v>0.68982926245486387</v>
       </c>
       <c r="D122">
         <v>-363</v>
       </c>
       <c r="E122">
-        <v>5652830475.671362</v>
+        <v>5652830475.6713619</v>
       </c>
       <c r="F122">
-        <v>-650730.1445753785</v>
+        <v>-27.964526961277169</v>
       </c>
       <c r="G122">
-        <v>269.930418796854</v>
-      </c>
-      <c r="H122">
-        <v>0.3101707375451361</v>
-      </c>
-    </row>
-    <row r="123" spans="1:8">
+        <v>0.31017073754513608</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>12936.5437</v>
       </c>
       <c r="B123">
-        <v>12936.5511</v>
+        <v>12936.551100000001</v>
       </c>
       <c r="C123">
-        <v>0.9393609154371304</v>
+        <v>0.93936091543713041</v>
       </c>
       <c r="D123">
         <v>-462</v>
@@ -3587,50 +3234,44 @@
         <v>1054536340.142622</v>
       </c>
       <c r="F123">
-        <v>215975076.2760331</v>
+        <v>9319.6894585363443</v>
       </c>
       <c r="G123">
-        <v>171.488168777924</v>
-      </c>
-      <c r="H123">
-        <v>0.06063908456286959</v>
-      </c>
-    </row>
-    <row r="124" spans="1:8">
+        <v>6.0639084562869587E-2</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124">
-        <v>13355.8281</v>
+        <v>13355.828100000001</v>
       </c>
       <c r="B124">
         <v>13355.8357</v>
       </c>
       <c r="C124">
-        <v>0.5855567927103711</v>
+        <v>0.58555679271037109</v>
       </c>
       <c r="D124">
         <v>-462</v>
       </c>
       <c r="E124">
-        <v>3940752423.939021</v>
+        <v>3940752423.9390211</v>
       </c>
       <c r="F124">
-        <v>-17138920.22262292</v>
+        <v>-763.54356642540745</v>
       </c>
       <c r="G124">
-        <v>170.5938907839318</v>
-      </c>
-      <c r="H124">
-        <v>0.4144432072896289</v>
-      </c>
-    </row>
-    <row r="125" spans="1:8">
+        <v>0.41444320728962891</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>13395.7647</v>
       </c>
       <c r="B125">
-        <v>13395.7769</v>
+        <v>13395.776900000001</v>
       </c>
       <c r="C125">
-        <v>0.5466335319904543</v>
+        <v>0.54663353199045428</v>
       </c>
       <c r="D125">
         <v>-360</v>
@@ -3639,47 +3280,41 @@
         <v>3645317858.151546</v>
       </c>
       <c r="F125">
-        <v>-27702535.8647331</v>
+        <v>-1237.8463170284731</v>
       </c>
       <c r="G125">
-        <v>273.0316685858902</v>
-      </c>
-      <c r="H125">
-        <v>0.4533664680095457</v>
-      </c>
-    </row>
-    <row r="126" spans="1:8">
+        <v>0.45336646800954572</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>14812.3724</v>
       </c>
       <c r="B126">
-        <v>14812.3713</v>
+        <v>14812.371300000001</v>
       </c>
       <c r="C126">
-        <v>0.5289910351287752</v>
+        <v>0.52899103512877521</v>
       </c>
       <c r="D126">
         <v>-655</v>
       </c>
       <c r="E126">
-        <v>4176362792.286147</v>
+        <v>4176362792.2861471</v>
       </c>
       <c r="F126">
-        <v>11991303.16024815</v>
+        <v>592.47532764970003</v>
       </c>
       <c r="G126">
-        <v>-22.26326037205379</v>
-      </c>
-      <c r="H126">
-        <v>0.4710089648712248</v>
-      </c>
-    </row>
-    <row r="127" spans="1:8">
+        <v>0.47100896487122479</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>14960.2394</v>
       </c>
       <c r="B127">
-        <v>14960.2499</v>
+        <v>14960.249900000001</v>
       </c>
       <c r="C127">
         <v>0.561277363811021</v>
@@ -3688,79 +3323,70 @@
         <v>-423</v>
       </c>
       <c r="E127">
-        <v>3416335965.676072</v>
+        <v>3416335965.6760721</v>
       </c>
       <c r="F127">
-        <v>-4225147.812217094</v>
+        <v>-210.84342000093281</v>
       </c>
       <c r="G127">
-        <v>210.4124623500545</v>
-      </c>
-      <c r="H127">
         <v>0.438722636188979</v>
       </c>
     </row>
-    <row r="128" spans="1:8">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128">
-        <v>15021.8064</v>
+        <v>15021.806399999999</v>
       </c>
       <c r="B128">
-        <v>15021.8206</v>
+        <v>15021.820599999999</v>
       </c>
       <c r="C128">
-        <v>0.7720337329699388</v>
+        <v>0.77203373296993882</v>
       </c>
       <c r="D128">
         <v>-350</v>
       </c>
       <c r="E128">
-        <v>2350162102.19848</v>
+        <v>2350162102.1984801</v>
       </c>
       <c r="F128">
-        <v>18432425.35255145</v>
+        <v>923.60090949626101</v>
       </c>
       <c r="G128">
-        <v>283.3915436144903</v>
-      </c>
-      <c r="H128">
         <v>0.2279662670300612</v>
       </c>
     </row>
-    <row r="129" spans="1:8">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129">
-        <v>15055.8625</v>
+        <v>15055.862499999999</v>
       </c>
       <c r="B129">
         <v>15055.8799</v>
       </c>
       <c r="C129">
-        <v>0.5379094265411464</v>
+        <v>0.53790942654114637</v>
       </c>
       <c r="D129">
         <v>-287</v>
       </c>
       <c r="E129">
-        <v>3532133521.254247</v>
+        <v>3532133521.2542472</v>
       </c>
       <c r="F129">
-        <v>-19652248.51544683</v>
+        <v>-986.95576061997099</v>
       </c>
       <c r="G129">
-        <v>346.4689432125126</v>
-      </c>
-      <c r="H129">
-        <v>0.4620905734588536</v>
-      </c>
-    </row>
-    <row r="130" spans="1:8">
+        <v>0.46209057345885363</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>15098.8248</v>
       </c>
       <c r="B130">
-        <v>15098.8286</v>
+        <v>15098.828600000001</v>
       </c>
       <c r="C130">
-        <v>0.6918845096885222</v>
+        <v>0.69188450968852222</v>
       </c>
       <c r="D130">
         <v>-558</v>
@@ -3769,24 +3395,21 @@
         <v>3476608258.668179</v>
       </c>
       <c r="F130">
-        <v>1998760.828410971</v>
+        <v>100.66613203648789</v>
       </c>
       <c r="G130">
-        <v>75.45033175572252</v>
-      </c>
-      <c r="H130">
-        <v>0.3081154903114778</v>
-      </c>
-    </row>
-    <row r="131" spans="1:8">
+        <v>0.30811549031147778</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A131">
-        <v>15126.5151</v>
+        <v>15126.515100000001</v>
       </c>
       <c r="B131">
-        <v>15126.5243</v>
+        <v>15126.524299999999</v>
       </c>
       <c r="C131">
-        <v>0.7081552046476831</v>
+        <v>0.70815520464768311</v>
       </c>
       <c r="D131">
         <v>-451</v>
@@ -3795,24 +3418,21 @@
         <v>3258857784.176424</v>
       </c>
       <c r="F131">
-        <v>-9281268.46865187</v>
+        <v>-468.30175102632597</v>
       </c>
       <c r="G131">
-        <v>182.3348335479448</v>
-      </c>
-      <c r="H131">
-        <v>0.2918447953523169</v>
-      </c>
-    </row>
-    <row r="132" spans="1:8">
+        <v>0.29184479535231689</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A132">
-        <v>15180.8648</v>
+        <v>15180.864799999999</v>
       </c>
       <c r="B132">
         <v>15180.8683</v>
       </c>
       <c r="C132">
-        <v>0.8834874681657605</v>
+        <v>0.88348746816576051</v>
       </c>
       <c r="D132">
         <v>-564</v>
@@ -3821,21 +3441,18 @@
         <v>1854800454.515697</v>
       </c>
       <c r="F132">
-        <v>-39080523.23495647</v>
+        <v>-1978.9566431486551</v>
       </c>
       <c r="G132">
-        <v>69.11817059749109</v>
-      </c>
-      <c r="H132">
         <v>0.1165125318342395</v>
       </c>
     </row>
-    <row r="133" spans="1:8">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A133">
-        <v>15211.6866</v>
+        <v>15211.686600000001</v>
       </c>
       <c r="B133">
-        <v>15211.7007</v>
+        <v>15211.700699999999</v>
       </c>
       <c r="C133">
         <v>0.5668591483740516</v>
@@ -3844,71 +3461,62 @@
         <v>-355</v>
       </c>
       <c r="E133">
-        <v>3705141813.06572</v>
+        <v>3705141813.0657201</v>
       </c>
       <c r="F133">
-        <v>-23251624.81021379</v>
+        <v>-1179.805388572071</v>
       </c>
       <c r="G133">
-        <v>277.8832990826441</v>
-      </c>
-      <c r="H133">
         <v>0.4331408516259484</v>
       </c>
     </row>
-    <row r="134" spans="1:8">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A134">
-        <v>15223.782</v>
+        <v>15223.781999999999</v>
       </c>
       <c r="B134">
         <v>15223.8017</v>
       </c>
       <c r="C134">
-        <v>0.6148569104063444</v>
+        <v>0.61485691040634438</v>
       </c>
       <c r="D134">
         <v>-245</v>
       </c>
       <c r="E134">
-        <v>3223982704.849172</v>
+        <v>3223982704.8491721</v>
       </c>
       <c r="F134">
-        <v>-14905797.98844591</v>
+        <v>-756.93336073304226</v>
       </c>
       <c r="G134">
-        <v>387.9398314054862</v>
-      </c>
-      <c r="H134">
-        <v>0.3851430895936556</v>
-      </c>
-    </row>
-    <row r="135" spans="1:8">
+        <v>0.38514308959365562</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A135">
-        <v>15228.8918</v>
+        <v>15228.891799999999</v>
       </c>
       <c r="B135">
-        <v>15228.8998</v>
+        <v>15228.899799999999</v>
       </c>
       <c r="C135">
-        <v>0.8230225882239158</v>
+        <v>0.82302258822391583</v>
       </c>
       <c r="D135">
         <v>-476</v>
       </c>
       <c r="E135">
-        <v>2355292363.132841</v>
+        <v>2355292363.1328411</v>
       </c>
       <c r="F135">
-        <v>-4009330.396214958</v>
+        <v>-203.66653409623771</v>
       </c>
       <c r="G135">
-        <v>157.4861582376646</v>
-      </c>
-      <c r="H135">
         <v>0.1769774117760842</v>
       </c>
     </row>
-    <row r="136" spans="1:8">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>15249.1397</v>
       </c>
@@ -3922,45 +3530,39 @@
         <v>-299</v>
       </c>
       <c r="E136">
-        <v>3630380395.531632</v>
+        <v>3630380395.5316319</v>
       </c>
       <c r="F136">
-        <v>-18025201.92779333</v>
+        <v>-916.8647222808471</v>
       </c>
       <c r="G136">
-        <v>334.2137252694796</v>
-      </c>
-      <c r="H136">
         <v>0.3773998264652626</v>
       </c>
     </row>
-    <row r="137" spans="1:8">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A137">
-        <v>15250.6653</v>
+        <v>15250.665300000001</v>
       </c>
       <c r="B137">
         <v>15250.6705</v>
       </c>
       <c r="C137">
-        <v>0.9092648263333029</v>
+        <v>0.90926482633330286</v>
       </c>
       <c r="D137">
         <v>-531</v>
       </c>
       <c r="E137">
-        <v>1107639082.173041</v>
+        <v>1107639082.1730411</v>
       </c>
       <c r="F137">
-        <v>-260580081.1625765</v>
+        <v>-13255.907047113609</v>
       </c>
       <c r="G137">
-        <v>102.2198540424131</v>
-      </c>
-      <c r="H137">
-        <v>0.09073517366669714</v>
-      </c>
-    </row>
-    <row r="138" spans="1:8">
+        <v>9.0735173666697144E-2</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>15339.5784</v>
       </c>
@@ -3968,25 +3570,22 @@
         <v>15339.6059</v>
       </c>
       <c r="C138">
-        <v>0.5465426509743899</v>
+        <v>0.54654265097438992</v>
       </c>
       <c r="D138">
         <v>-96</v>
       </c>
       <c r="E138">
-        <v>3256569347.414473</v>
+        <v>3256569347.4144731</v>
       </c>
       <c r="F138">
-        <v>20886780.63261012</v>
+        <v>1068.722627518508</v>
       </c>
       <c r="G138">
-        <v>537.452358866126</v>
-      </c>
-      <c r="H138">
-        <v>0.4534573490256101</v>
-      </c>
-    </row>
-    <row r="139" spans="1:8">
+        <v>0.45345734902561008</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>15347.9951</v>
       </c>
@@ -3994,7 +3593,7 @@
         <v>15348.0003</v>
       </c>
       <c r="C139">
-        <v>0.7757252771520285</v>
+        <v>0.77572527715202855</v>
       </c>
       <c r="D139">
         <v>-531</v>
@@ -4003,16 +3602,13 @@
         <v>2755933012.006021</v>
       </c>
       <c r="F139">
-        <v>-40158856.45263437</v>
+        <v>-2055.9494558154938</v>
       </c>
       <c r="G139">
-        <v>101.5716236259524</v>
-      </c>
-      <c r="H139">
-        <v>0.2242747228479715</v>
-      </c>
-    </row>
-    <row r="140" spans="1:8">
+        <v>0.22427472284797151</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>15494.572</v>
       </c>
@@ -4020,7 +3616,7 @@
         <v>15494.5846</v>
       </c>
       <c r="C140">
-        <v>0.9272412941322346</v>
+        <v>0.92724129413223455</v>
       </c>
       <c r="D140">
         <v>-389</v>
@@ -4029,24 +3625,21 @@
         <v>1496411122.723968</v>
       </c>
       <c r="F140">
-        <v>102506662.6875892</v>
+        <v>5297.9923767011996</v>
       </c>
       <c r="G140">
-        <v>243.7876290177686</v>
-      </c>
-      <c r="H140">
-        <v>0.07275870586776545</v>
-      </c>
-    </row>
-    <row r="141" spans="1:8">
+        <v>7.275870586776545E-2</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>15518.5211</v>
       </c>
       <c r="B141">
-        <v>15518.5341</v>
+        <v>15518.534100000001</v>
       </c>
       <c r="C141">
-        <v>0.9042687726424414</v>
+        <v>0.90426877264244143</v>
       </c>
       <c r="D141">
         <v>-382</v>
@@ -4055,24 +3648,21 @@
         <v>1369355575.743196</v>
       </c>
       <c r="F141">
-        <v>99287991.6351856</v>
+        <v>5139.5692012743784</v>
       </c>
       <c r="G141">
-        <v>251.1387476538749</v>
-      </c>
-      <c r="H141">
-        <v>0.09573122735755857</v>
-      </c>
-    </row>
-    <row r="142" spans="1:8">
+        <v>9.5731227357558568E-2</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A142">
-        <v>15523.6066</v>
+        <v>15523.606599999999</v>
       </c>
       <c r="B142">
         <v>15523.609</v>
       </c>
       <c r="C142">
-        <v>0.8886029596826526</v>
+        <v>0.88860295968265257</v>
       </c>
       <c r="D142">
         <v>-587</v>
@@ -4081,68 +3671,59 @@
         <v>1331376628.093632</v>
       </c>
       <c r="F142">
-        <v>59480893.18530277</v>
+        <v>3079.9911877016089</v>
       </c>
       <c r="G142">
-        <v>46.34888772717395</v>
-      </c>
-      <c r="H142">
         <v>0.1113970403173474</v>
       </c>
     </row>
-    <row r="143" spans="1:8">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A143">
-        <v>15536.003</v>
+        <v>15536.003000000001</v>
       </c>
       <c r="B143">
         <v>15536.0121</v>
       </c>
       <c r="C143">
-        <v>0.7362798031491248</v>
+        <v>0.73627980314912478</v>
       </c>
       <c r="D143">
         <v>-457</v>
       </c>
       <c r="E143">
-        <v>3060273067.410341</v>
+        <v>3060273067.4103408</v>
       </c>
       <c r="F143">
-        <v>-11301427.42831764</v>
+        <v>-585.66888054807146</v>
       </c>
       <c r="G143">
-        <v>175.5993074487081</v>
-      </c>
-      <c r="H143">
-        <v>0.2637201968508752</v>
-      </c>
-    </row>
-    <row r="144" spans="1:8">
+        <v>0.26372019685087522</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A144">
-        <v>15538.4919</v>
+        <v>15538.491900000001</v>
       </c>
       <c r="B144">
         <v>15538.5018</v>
       </c>
       <c r="C144">
-        <v>0.6938903369409034</v>
+        <v>0.69389033694090341</v>
       </c>
       <c r="D144">
         <v>-442</v>
       </c>
       <c r="E144">
-        <v>3785816998.200178</v>
+        <v>3785816998.2001781</v>
       </c>
       <c r="F144">
-        <v>-15407605.52427121</v>
+        <v>-798.58949010844765</v>
       </c>
       <c r="G144">
-        <v>191.0060096595961</v>
-      </c>
-      <c r="H144">
-        <v>0.3061096630590966</v>
-      </c>
-    </row>
-    <row r="145" spans="1:8">
+        <v>0.30610966305909659</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>15546.3307</v>
       </c>
@@ -4150,51 +3731,45 @@
         <v>15546.3303</v>
       </c>
       <c r="C145">
-        <v>0.7283551412905589</v>
+        <v>0.72835514129055889</v>
       </c>
       <c r="D145">
         <v>-641</v>
       </c>
       <c r="E145">
-        <v>3349839984.879492</v>
+        <v>3349839984.8794918</v>
       </c>
       <c r="F145">
-        <v>11518568.90202348</v>
+        <v>597.31815112628783</v>
       </c>
       <c r="G145">
-        <v>-7.713523254235525</v>
-      </c>
-      <c r="H145">
-        <v>0.2716448587094411</v>
-      </c>
-    </row>
-    <row r="146" spans="1:8">
+        <v>0.27164485870944111</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A146">
-        <v>15555.6848</v>
+        <v>15555.684800000001</v>
       </c>
       <c r="B146">
         <v>15555.7006</v>
       </c>
       <c r="C146">
-        <v>0.8446801700024277</v>
+        <v>0.84468017000242768</v>
       </c>
       <c r="D146">
         <v>-328</v>
       </c>
       <c r="E146">
-        <v>2115502168.66674</v>
+        <v>2115502168.6667399</v>
       </c>
       <c r="F146">
-        <v>-18044504.93170052</v>
+        <v>-936.29745746558012</v>
       </c>
       <c r="G146">
-        <v>304.5009523394917</v>
-      </c>
-      <c r="H146">
         <v>0.1553198299975723</v>
       </c>
     </row>
-    <row r="147" spans="1:8">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>15592.5237</v>
       </c>
@@ -4202,33 +3777,30 @@
         <v>15592.5219</v>
       </c>
       <c r="C147">
-        <v>0.7150271949777279</v>
+        <v>0.71502719497772793</v>
       </c>
       <c r="D147">
         <v>-668</v>
       </c>
       <c r="E147">
-        <v>3345003900.470722</v>
+        <v>3345003900.4707222</v>
       </c>
       <c r="F147">
-        <v>7466818.371781709</v>
+        <v>388.35709798052568</v>
       </c>
       <c r="G147">
-        <v>-34.60802334615429</v>
-      </c>
-      <c r="H147">
-        <v>0.2849728050222721</v>
-      </c>
-    </row>
-    <row r="148" spans="1:8">
+        <v>0.28497280502227212</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A148">
-        <v>15603.1385</v>
+        <v>15603.138499999999</v>
       </c>
       <c r="B148">
         <v>15603.1523</v>
       </c>
       <c r="C148">
-        <v>0.9289857869195556</v>
+        <v>0.92898578691955558</v>
       </c>
       <c r="D148">
         <v>-368</v>
@@ -4237,16 +3809,13 @@
         <v>641019393.6751802</v>
       </c>
       <c r="F148">
-        <v>176514311.1066101</v>
+        <v>9186.9545274751999</v>
       </c>
       <c r="G148">
-        <v>265.147676599972</v>
-      </c>
-      <c r="H148">
-        <v>0.07101421308044442</v>
-      </c>
-    </row>
-    <row r="149" spans="1:8">
+        <v>7.1014213080444422E-2</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>15615.4038</v>
       </c>
@@ -4263,50 +3832,44 @@
         <v>2128410984.442255</v>
       </c>
       <c r="F149">
-        <v>-29292744.5491517</v>
+        <v>-1525.783588664053</v>
       </c>
       <c r="G149">
-        <v>247.660755848954</v>
-      </c>
-      <c r="H149">
         <v>0.161362117607041</v>
       </c>
     </row>
-    <row r="150" spans="1:8">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>15617.8987</v>
       </c>
       <c r="B150">
-        <v>15617.9039</v>
+        <v>15617.903899999999</v>
       </c>
       <c r="C150">
-        <v>0.8210097274267024</v>
+        <v>0.82100972742670242</v>
       </c>
       <c r="D150">
         <v>-533</v>
       </c>
       <c r="E150">
-        <v>1920806518.761335</v>
+        <v>1920806518.7613349</v>
       </c>
       <c r="F150">
-        <v>-14444204.9751977</v>
+        <v>-752.48125559762912</v>
       </c>
       <c r="G150">
-        <v>99.81629483784745</v>
-      </c>
-      <c r="H150">
-        <v>0.1789902725732976</v>
-      </c>
-    </row>
-    <row r="151" spans="1:8">
+        <v>0.17899027257329761</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A151">
-        <v>15625.9278</v>
+        <v>15625.927799999999</v>
       </c>
       <c r="B151">
         <v>15625.947</v>
       </c>
       <c r="C151">
-        <v>0.5556577766281227</v>
+        <v>0.55565777662812266</v>
       </c>
       <c r="D151">
         <v>-265</v>
@@ -4315,24 +3878,21 @@
         <v>3308374422.757637</v>
       </c>
       <c r="F151">
-        <v>-12927320.51711405</v>
+        <v>-673.80489355885265</v>
       </c>
       <c r="G151">
-        <v>368.3630993007404</v>
-      </c>
-      <c r="H151">
-        <v>0.4443422233718773</v>
-      </c>
-    </row>
-    <row r="152" spans="1:8">
+        <v>0.44434222337187729</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>15636.2214</v>
       </c>
       <c r="B152">
-        <v>15636.2334</v>
+        <v>15636.233399999999</v>
       </c>
       <c r="C152">
-        <v>0.5715204320181916</v>
+        <v>0.57152043201819158</v>
       </c>
       <c r="D152">
         <v>-403</v>
@@ -4341,68 +3901,59 @@
         <v>3708052043.393218</v>
       </c>
       <c r="F152">
-        <v>-15545737.79064793</v>
+        <v>-810.81687675335502</v>
       </c>
       <c r="G152">
-        <v>230.0753746088103</v>
-      </c>
-      <c r="H152">
-        <v>0.4284795679818084</v>
-      </c>
-    </row>
-    <row r="153" spans="1:8">
+        <v>0.42847956798180842</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A153">
-        <v>15652.791</v>
+        <v>15652.790999999999</v>
       </c>
       <c r="B153">
         <v>15652.7932</v>
       </c>
       <c r="C153">
-        <v>0.725048505652951</v>
+        <v>0.72504850565295098</v>
       </c>
       <c r="D153">
         <v>-591</v>
       </c>
       <c r="E153">
-        <v>3638577979.461855</v>
+        <v>3638577979.4618549</v>
       </c>
       <c r="F153">
-        <v>-5329848.285221979</v>
+        <v>-278.28256105079947</v>
       </c>
       <c r="G153">
-        <v>42.13583432360907</v>
-      </c>
-      <c r="H153">
-        <v>0.274951494347049</v>
-      </c>
-    </row>
-    <row r="154" spans="1:8">
+        <v>0.27495149434704902</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>15657.151</v>
       </c>
       <c r="B154">
-        <v>15657.1652</v>
+        <v>15657.165199999999</v>
       </c>
       <c r="C154">
-        <v>0.7795120957145266</v>
+        <v>0.77951209571452662</v>
       </c>
       <c r="D154">
         <v>-361</v>
       </c>
       <c r="E154">
-        <v>2776986058.737023</v>
+        <v>2776986058.7370229</v>
       </c>
       <c r="F154">
-        <v>-5524094.789445193</v>
+        <v>-288.50513877438038</v>
       </c>
       <c r="G154">
-        <v>271.8919236143388</v>
-      </c>
-      <c r="H154">
-        <v>0.2204879042854734</v>
-      </c>
-    </row>
-    <row r="155" spans="1:8">
+        <v>0.22048790428547341</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A155">
         <v>15666.2978</v>
       </c>
@@ -4410,7 +3961,7 @@
         <v>15666.3112</v>
       </c>
       <c r="C155">
-        <v>0.6238602646789065</v>
+        <v>0.62386026467890654</v>
       </c>
       <c r="D155">
         <v>-377</v>
@@ -4419,42 +3970,36 @@
         <v>3431266749.599977</v>
       </c>
       <c r="F155">
-        <v>-6144866.720842819</v>
+        <v>-321.1134628718616</v>
       </c>
       <c r="G155">
-        <v>256.424267459517</v>
-      </c>
-      <c r="H155">
-        <v>0.3761397353210935</v>
-      </c>
-    </row>
-    <row r="156" spans="1:8">
+        <v>0.37613973532109352</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A156">
-        <v>15669.5259</v>
+        <v>15669.525900000001</v>
       </c>
       <c r="B156">
-        <v>15669.5287</v>
+        <v>15669.528700000001</v>
       </c>
       <c r="C156">
-        <v>0.8153067985721358</v>
+        <v>0.81530679857213584</v>
       </c>
       <c r="D156">
         <v>-579</v>
       </c>
       <c r="E156">
-        <v>2161430199.950818</v>
+        <v>2161430199.9508181</v>
       </c>
       <c r="F156">
-        <v>-39521753.0038707</v>
+        <v>-2065.7198886853362</v>
       </c>
       <c r="G156">
-        <v>53.57015187109182</v>
-      </c>
-      <c r="H156">
-        <v>0.1846932014278642</v>
-      </c>
-    </row>
-    <row r="157" spans="1:8">
+        <v>0.18469320142786419</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A157">
         <v>15680.8729</v>
       </c>
@@ -4462,7 +4007,7 @@
         <v>15680.8745</v>
       </c>
       <c r="C157">
-        <v>0.8904647697890259</v>
+        <v>0.89046476978902589</v>
       </c>
       <c r="D157">
         <v>-602</v>
@@ -4471,16 +4016,13 @@
         <v>2958394824.958137</v>
       </c>
       <c r="F157">
-        <v>130391513.3155631</v>
+        <v>6820.2281331788008</v>
       </c>
       <c r="G157">
-        <v>30.58936425919826</v>
-      </c>
-      <c r="H157">
         <v>0.1095352302109741</v>
       </c>
     </row>
-    <row r="158" spans="1:8">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>15681.8073</v>
       </c>
@@ -4488,7 +4030,7 @@
         <v>15681.822</v>
       </c>
       <c r="C158">
-        <v>0.7040309607855111</v>
+        <v>0.70403096078551108</v>
       </c>
       <c r="D158">
         <v>-352</v>
@@ -4497,21 +4039,18 @@
         <v>3358313621.082551</v>
       </c>
       <c r="F158">
-        <v>-940112.4217698813</v>
+        <v>-49.176272667220339</v>
       </c>
       <c r="G158">
-        <v>281.0230382164584</v>
-      </c>
-      <c r="H158">
-        <v>0.2959690392144889</v>
-      </c>
-    </row>
-    <row r="159" spans="1:8">
+        <v>0.29596903921448892</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A159">
-        <v>15686.8036</v>
+        <v>15686.803599999999</v>
       </c>
       <c r="B159">
-        <v>15686.8198</v>
+        <v>15686.819799999999</v>
       </c>
       <c r="C159">
         <v>0.8653201613196303</v>
@@ -4523,44 +4062,38 @@
         <v>1497438084.829989</v>
       </c>
       <c r="F159">
-        <v>-13984483.06792466</v>
+        <v>-731.74644667907319</v>
       </c>
       <c r="G159">
-        <v>309.6002183101011</v>
-      </c>
-      <c r="H159">
         <v>0.1346798386803697</v>
       </c>
     </row>
-    <row r="160" spans="1:8">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A160">
-        <v>15690.7319</v>
+        <v>15690.731900000001</v>
       </c>
       <c r="B160">
-        <v>15690.7342</v>
+        <v>15690.734200000001</v>
       </c>
       <c r="C160">
-        <v>0.7003927285955432</v>
+        <v>0.70039272859554325</v>
       </c>
       <c r="D160">
         <v>-589</v>
       </c>
       <c r="E160">
-        <v>3691882257.913296</v>
+        <v>3691882257.9132962</v>
       </c>
       <c r="F160">
-        <v>70925485.27770038</v>
+        <v>3712.1445446716671</v>
       </c>
       <c r="G160">
-        <v>43.94458190379509</v>
-      </c>
-      <c r="H160">
-        <v>0.2996072714044568</v>
-      </c>
-    </row>
-    <row r="161" spans="1:8">
+        <v>0.29960727140445681</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A161">
-        <v>15696.1452</v>
+        <v>15696.145200000001</v>
       </c>
       <c r="B161">
         <v>15696.1648</v>
@@ -4575,16 +4108,13 @@
         <v>3389258173.328023</v>
       </c>
       <c r="F161">
-        <v>-13139329.48703831</v>
+        <v>-687.93285316754987</v>
       </c>
       <c r="G161">
-        <v>374.3551108861444</v>
-      </c>
-      <c r="H161">
         <v>0.3678593444319519</v>
       </c>
     </row>
-    <row r="162" spans="1:8">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>15727.8899</v>
       </c>
@@ -4592,7 +4122,7 @@
         <v>15727.903</v>
       </c>
       <c r="C162">
-        <v>0.5945175075354717</v>
+        <v>0.59451750753547172</v>
       </c>
       <c r="D162">
         <v>-383</v>
@@ -4601,24 +4131,21 @@
         <v>3360735596.695724</v>
       </c>
       <c r="F162">
-        <v>-1424466.953564628</v>
+        <v>-74.731293181398073</v>
       </c>
       <c r="G162">
-        <v>249.7017225159084</v>
-      </c>
-      <c r="H162">
-        <v>0.4054824924645283</v>
-      </c>
-    </row>
-    <row r="163" spans="1:8">
+        <v>0.40548249246452828</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>15778.3807</v>
       </c>
       <c r="B163">
-        <v>15778.3859</v>
+        <v>15778.385899999999</v>
       </c>
       <c r="C163">
-        <v>0.6276711896693961</v>
+        <v>0.62767118966939606</v>
       </c>
       <c r="D163">
         <v>-534</v>
@@ -4627,120 +4154,105 @@
         <v>2775194890.509315</v>
       </c>
       <c r="F163">
-        <v>-46096031.02674194</v>
+        <v>-2426.0815994187142</v>
       </c>
       <c r="G163">
-        <v>98.80106273223207</v>
-      </c>
-      <c r="H163">
-        <v>0.3723288103306039</v>
-      </c>
-    </row>
-    <row r="164" spans="1:8">
+        <v>0.37232881033060389</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>15793.3148</v>
       </c>
       <c r="B164">
-        <v>15793.3319</v>
+        <v>15793.331899999999</v>
       </c>
       <c r="C164">
-        <v>0.6766827877443455</v>
+        <v>0.67668278774434554</v>
       </c>
       <c r="D164">
         <v>-308</v>
       </c>
       <c r="E164">
-        <v>3272568222.625025</v>
+        <v>3272568222.6250248</v>
       </c>
       <c r="F164">
-        <v>-1256206.585799897</v>
+        <v>-66.178074247963877</v>
       </c>
       <c r="G164">
-        <v>324.5962672596718</v>
-      </c>
-      <c r="H164">
-        <v>0.3233172122556545</v>
-      </c>
-    </row>
-    <row r="165" spans="1:8">
+        <v>0.32331721225565452</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A165">
-        <v>15820.9574</v>
+        <v>15820.957399999999</v>
       </c>
       <c r="B165">
         <v>15820.9627</v>
       </c>
       <c r="C165">
-        <v>0.8387097973324181</v>
+        <v>0.83870979733241813</v>
       </c>
       <c r="D165">
         <v>-533</v>
       </c>
       <c r="E165">
-        <v>1984738847.859315</v>
+        <v>1984738847.8593149</v>
       </c>
       <c r="F165">
-        <v>-3376419.004386254</v>
+        <v>-178.18393259234711</v>
       </c>
       <c r="G165">
-        <v>100.4300806716848</v>
-      </c>
-      <c r="H165">
         <v>0.1612902026675819</v>
       </c>
     </row>
-    <row r="166" spans="1:8">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A166">
-        <v>15822.4644</v>
+        <v>15822.464400000001</v>
       </c>
       <c r="B166">
         <v>15822.4863</v>
       </c>
       <c r="C166">
-        <v>0.5584354708890029</v>
+        <v>0.55843547088900292</v>
       </c>
       <c r="D166">
         <v>-218</v>
       </c>
       <c r="E166">
-        <v>2977581355.170902</v>
+        <v>2977581355.1709018</v>
       </c>
       <c r="F166">
-        <v>-4201763.757616004</v>
+        <v>-221.7612475451792</v>
       </c>
       <c r="G166">
-        <v>414.9451478422461</v>
-      </c>
-      <c r="H166">
-        <v>0.4415645291109971</v>
-      </c>
-    </row>
-    <row r="167" spans="1:8">
+        <v>0.44156452911099708</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A167">
-        <v>15823.4608</v>
+        <v>15823.460800000001</v>
       </c>
       <c r="B167">
-        <v>15823.4718</v>
+        <v>15823.471799999999</v>
       </c>
       <c r="C167">
-        <v>0.7449804701752084</v>
+        <v>0.74498047017520841</v>
       </c>
       <c r="D167">
         <v>-425</v>
       </c>
       <c r="E167">
-        <v>2551710361.498037</v>
+        <v>2551710361.4980369</v>
       </c>
       <c r="F167">
-        <v>25374146.47156611</v>
+        <v>1339.283495723884</v>
       </c>
       <c r="G167">
-        <v>208.4068130961335</v>
-      </c>
-      <c r="H167">
-        <v>0.2550195298247916</v>
-      </c>
-    </row>
-    <row r="168" spans="1:8">
+        <v>0.25501952982479159</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A168">
         <v>15826.0352</v>
       </c>
@@ -4748,25 +4260,22 @@
         <v>15826.0443</v>
       </c>
       <c r="C168">
-        <v>0.818759182845343</v>
+        <v>0.81875918284534299</v>
       </c>
       <c r="D168">
         <v>-461</v>
       </c>
       <c r="E168">
-        <v>2189644938.355878</v>
+        <v>2189644938.3558779</v>
       </c>
       <c r="F168">
-        <v>17936058.31621805</v>
+        <v>946.84454496800663</v>
       </c>
       <c r="G168">
-        <v>172.3812270593169</v>
-      </c>
-      <c r="H168">
-        <v>0.181240817154657</v>
-      </c>
-    </row>
-    <row r="169" spans="1:8">
+        <v>0.18124081715465701</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A169">
         <v>15827.1448</v>
       </c>
@@ -4774,33 +4283,30 @@
         <v>15827.1567</v>
       </c>
       <c r="C169">
-        <v>0.6380249166852207</v>
+        <v>0.63802491668522066</v>
       </c>
       <c r="D169">
         <v>-408</v>
       </c>
       <c r="E169">
-        <v>4022960594.522149</v>
+        <v>4022960594.5221491</v>
       </c>
       <c r="F169">
-        <v>12832525.2108562</v>
+        <v>677.47664075298917</v>
       </c>
       <c r="G169">
-        <v>225.4058009455241</v>
-      </c>
-      <c r="H169">
-        <v>0.3619750833147793</v>
-      </c>
-    </row>
-    <row r="170" spans="1:8">
+        <v>0.36197508331477929</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>15839.4915</v>
       </c>
       <c r="B170">
-        <v>15839.5143</v>
+        <v>15839.514300000001</v>
       </c>
       <c r="C170">
-        <v>0.6215357095704941</v>
+        <v>0.62153570957049409</v>
       </c>
       <c r="D170">
         <v>-201</v>
@@ -4809,24 +4315,21 @@
         <v>3121919735.65976</v>
       </c>
       <c r="F170">
-        <v>2315641.968682407</v>
+        <v>122.34678724514519</v>
       </c>
       <c r="G170">
-        <v>431.5333003021923</v>
-      </c>
-      <c r="H170">
-        <v>0.3784642904295059</v>
-      </c>
-    </row>
-    <row r="171" spans="1:8">
+        <v>0.37846429042950591</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A171">
-        <v>15857.6516</v>
+        <v>15857.651599999999</v>
       </c>
       <c r="B171">
         <v>15857.6517</v>
       </c>
       <c r="C171">
-        <v>0.8600592139412852</v>
+        <v>0.86005921394128515</v>
       </c>
       <c r="D171">
         <v>-631</v>
@@ -4835,42 +4338,36 @@
         <v>1731865508.150192</v>
       </c>
       <c r="F171">
-        <v>-73051761.23565413</v>
+        <v>-3864.1044990750402</v>
       </c>
       <c r="G171">
-        <v>1.890522443555685</v>
-      </c>
-      <c r="H171">
-        <v>0.1399407860587148</v>
-      </c>
-    </row>
-    <row r="172" spans="1:8">
+        <v>0.13994078605871479</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>15868.0489</v>
       </c>
       <c r="B172">
-        <v>15868.068</v>
+        <v>15868.067999999999</v>
       </c>
       <c r="C172">
-        <v>0.7328976123610165</v>
+        <v>0.73289761236101647</v>
       </c>
       <c r="D172">
         <v>-272</v>
       </c>
       <c r="E172">
-        <v>3139864006.512664</v>
+        <v>3139864006.5126638</v>
       </c>
       <c r="F172">
-        <v>-26694836.80401955</v>
+        <v>-1412.9624490256019</v>
       </c>
       <c r="G172">
-        <v>360.8531826447532</v>
-      </c>
-      <c r="H172">
-        <v>0.2671023876389835</v>
-      </c>
-    </row>
-    <row r="173" spans="1:8">
+        <v>0.26710238763898347</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>15872.8622</v>
       </c>
@@ -4878,33 +4375,30 @@
         <v>15872.8797</v>
       </c>
       <c r="C173">
-        <v>0.6294059097535925</v>
+        <v>0.62940590975359245</v>
       </c>
       <c r="D173">
         <v>-302</v>
       </c>
       <c r="E173">
-        <v>3555038684.349282</v>
+        <v>3555038684.3492818</v>
       </c>
       <c r="F173">
-        <v>-11382656.53319679</v>
+        <v>-602.66872296651195</v>
       </c>
       <c r="G173">
-        <v>330.5243848898632</v>
-      </c>
-      <c r="H173">
-        <v>0.3705940902464075</v>
-      </c>
-    </row>
-    <row r="174" spans="1:8">
+        <v>0.37059409024640749</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>15882.7876</v>
       </c>
       <c r="B174">
-        <v>15882.7964</v>
+        <v>15882.796399999999</v>
       </c>
       <c r="C174">
-        <v>0.7156644136821264</v>
+        <v>0.71566441368212641</v>
       </c>
       <c r="D174">
         <v>-467</v>
@@ -4913,47 +4407,41 @@
         <v>3312740761.39504</v>
       </c>
       <c r="F174">
-        <v>7834604.476762424</v>
+        <v>415.07190877679159</v>
       </c>
       <c r="G174">
-        <v>166.1026827974451</v>
-      </c>
-      <c r="H174">
-        <v>0.2843355863178736</v>
-      </c>
-    </row>
-    <row r="175" spans="1:8">
+        <v>0.28433558631787359</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A175">
-        <v>15899.5732</v>
+        <v>15899.573200000001</v>
       </c>
       <c r="B175">
         <v>15899.5906</v>
       </c>
       <c r="C175">
-        <v>0.6737957051372857</v>
+        <v>0.67379570513728571</v>
       </c>
       <c r="D175">
         <v>-305</v>
       </c>
       <c r="E175">
-        <v>3151944383.743469</v>
+        <v>3151944383.7434692</v>
       </c>
       <c r="F175">
-        <v>7595046.538135923</v>
+        <v>402.80576552832582</v>
       </c>
       <c r="G175">
-        <v>328.0835720292703</v>
-      </c>
-      <c r="H175">
-        <v>0.3262042948627143</v>
-      </c>
-    </row>
-    <row r="176" spans="1:8">
+        <v>0.32620429486271429</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A176">
-        <v>15905.8653</v>
+        <v>15905.865299999999</v>
       </c>
       <c r="B176">
-        <v>15905.8697</v>
+        <v>15905.869699999999</v>
       </c>
       <c r="C176">
         <v>0.7966381337994477</v>
@@ -4962,53 +4450,47 @@
         <v>-550</v>
       </c>
       <c r="E176">
-        <v>2723534864.191213</v>
+        <v>2723534864.1912131</v>
       </c>
       <c r="F176">
-        <v>-9337295.743194398</v>
+        <v>-495.40208727203787</v>
       </c>
       <c r="G176">
-        <v>82.93084284040249</v>
-      </c>
-      <c r="H176">
         <v>0.2033618662005523</v>
       </c>
     </row>
-    <row r="177" spans="1:8">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A177">
-        <v>15910.3901</v>
+        <v>15910.390100000001</v>
       </c>
       <c r="B177">
         <v>15910.4038</v>
       </c>
       <c r="C177">
-        <v>0.6468542558777182</v>
+        <v>0.64685425587771817</v>
       </c>
       <c r="D177">
         <v>-375</v>
       </c>
       <c r="E177">
-        <v>3508808338.613146</v>
+        <v>3508808338.6131458</v>
       </c>
       <c r="F177">
-        <v>-34674361.21255974</v>
+        <v>-1840.2167021789551</v>
       </c>
       <c r="G177">
-        <v>258.1430529977978</v>
-      </c>
-      <c r="H177">
-        <v>0.3531457441222818</v>
-      </c>
-    </row>
-    <row r="178" spans="1:8">
+        <v>0.35314574412228178</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A178">
-        <v>15915.6521</v>
+        <v>15915.652099999999</v>
       </c>
       <c r="B178">
         <v>15915.6644</v>
       </c>
       <c r="C178">
-        <v>0.6789471003082453</v>
+        <v>0.67894710030824534</v>
       </c>
       <c r="D178">
         <v>-401</v>
@@ -5017,42 +4499,36 @@
         <v>3318848889.865634</v>
       </c>
       <c r="F178">
-        <v>-19919719.44406146</v>
+        <v>-1057.516829238702</v>
       </c>
       <c r="G178">
-        <v>231.6868458079414</v>
-      </c>
-      <c r="H178">
-        <v>0.3210528996917547</v>
-      </c>
-    </row>
-    <row r="179" spans="1:8">
+        <v>0.32105289969175471</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A179">
-        <v>15975.6174</v>
+        <v>15975.617399999999</v>
       </c>
       <c r="B179">
-        <v>15975.6171</v>
+        <v>15975.617099999999</v>
       </c>
       <c r="C179">
-        <v>0.8738257902228344</v>
+        <v>0.87382579022283435</v>
       </c>
       <c r="D179">
         <v>-639</v>
       </c>
       <c r="E179">
-        <v>1720394457.41666</v>
+        <v>1720394457.4166601</v>
       </c>
       <c r="F179">
-        <v>-73252353.96180697</v>
+        <v>-3903.5390228779411</v>
       </c>
       <c r="G179">
-        <v>-5.629687746690727</v>
-      </c>
-      <c r="H179">
-        <v>0.1261742097771656</v>
-      </c>
-    </row>
-    <row r="180" spans="1:8">
+        <v>0.12617420977716559</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A180">
         <v>15985.0942</v>
       </c>
@@ -5060,25 +4536,22 @@
         <v>15985.1216</v>
       </c>
       <c r="C180">
-        <v>0.5841785243732169</v>
+        <v>0.58417852437321693</v>
       </c>
       <c r="D180">
         <v>-119</v>
       </c>
       <c r="E180">
-        <v>3133499126.051802</v>
+        <v>3133499126.0518022</v>
       </c>
       <c r="F180">
-        <v>-26487956.92375318</v>
+        <v>-1412.3544507639231</v>
       </c>
       <c r="G180">
-        <v>513.8733151715904</v>
-      </c>
-      <c r="H180">
-        <v>0.4158214756267831</v>
-      </c>
-    </row>
-    <row r="181" spans="1:8">
+        <v>0.41582147562678312</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A181">
         <v>16002.0995</v>
       </c>
@@ -5086,7 +4559,7 @@
         <v>16002.1047</v>
       </c>
       <c r="C181">
-        <v>0.795329776619093</v>
+        <v>0.79532977661909299</v>
       </c>
       <c r="D181">
         <v>-536</v>
@@ -5095,68 +4568,59 @@
         <v>2558647282.837667</v>
       </c>
       <c r="F181">
-        <v>-8682077.774653837</v>
+        <v>-463.42565950592962</v>
       </c>
       <c r="G181">
-        <v>97.41976553934342</v>
-      </c>
-      <c r="H181">
-        <v>0.204670223380907</v>
-      </c>
-    </row>
-    <row r="182" spans="1:8">
+        <v>0.20467022338090701</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A182">
-        <v>16013.9898</v>
+        <v>16013.989799999999</v>
       </c>
       <c r="B182">
         <v>16013.992</v>
       </c>
       <c r="C182">
-        <v>0.6662570606194367</v>
+        <v>0.66625706061943668</v>
       </c>
       <c r="D182">
         <v>-592</v>
       </c>
       <c r="E182">
-        <v>3626362545.983729</v>
+        <v>3626362545.9837289</v>
       </c>
       <c r="F182">
-        <v>-21895157.18864502</v>
+        <v>-1169.5720245827661</v>
       </c>
       <c r="G182">
-        <v>41.18545194646949</v>
-      </c>
-      <c r="H182">
-        <v>0.3337429393805633</v>
-      </c>
-    </row>
-    <row r="183" spans="1:8">
+        <v>0.33374293938056332</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A183">
-        <v>16033.8018</v>
+        <v>16033.801799999999</v>
       </c>
       <c r="B183">
         <v>16033.8164</v>
       </c>
       <c r="C183">
-        <v>0.8906610624103055</v>
+        <v>0.89066106241030552</v>
       </c>
       <c r="D183">
         <v>-360</v>
       </c>
       <c r="E183">
-        <v>1277680401.84855</v>
+        <v>1277680401.8485501</v>
       </c>
       <c r="F183">
-        <v>-51875006.56585878</v>
+        <v>-2774.433808557566</v>
       </c>
       <c r="G183">
-        <v>272.9839087463706</v>
-      </c>
-      <c r="H183">
         <v>0.1093389375896945</v>
       </c>
     </row>
-    <row r="184" spans="1:8">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>16045.0391</v>
       </c>
@@ -5164,25 +4628,22 @@
         <v>16045.0506</v>
       </c>
       <c r="C184">
-        <v>0.6296260972754738</v>
+        <v>0.62962609727547381</v>
       </c>
       <c r="D184">
         <v>-418</v>
       </c>
       <c r="E184">
-        <v>3492410645.778711</v>
+        <v>3492410645.7787108</v>
       </c>
       <c r="F184">
-        <v>-7629008.36744724</v>
+        <v>-408.30855485868949</v>
       </c>
       <c r="G184">
-        <v>214.870979469381</v>
-      </c>
-      <c r="H184">
-        <v>0.3703739027245262</v>
-      </c>
-    </row>
-    <row r="185" spans="1:8">
+        <v>0.37037390272452619</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A185">
         <v>16075.7929</v>
       </c>
@@ -5190,25 +4651,22 @@
         <v>16075.8086</v>
       </c>
       <c r="C185">
-        <v>0.7452319973503224</v>
+        <v>0.74523199735032242</v>
       </c>
       <c r="D185">
         <v>-340</v>
       </c>
       <c r="E185">
-        <v>2869088868.426933</v>
+        <v>2869088868.4269328</v>
       </c>
       <c r="F185">
-        <v>21402897.52163912</v>
+        <v>1147.690259917362</v>
       </c>
       <c r="G185">
-        <v>292.7844131468875</v>
-      </c>
-      <c r="H185">
-        <v>0.2547680026496776</v>
-      </c>
-    </row>
-    <row r="186" spans="1:8">
+        <v>0.25476800264967758</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>16080.3141</v>
       </c>
@@ -5216,7 +4674,7 @@
         <v>16080.3213</v>
       </c>
       <c r="C186">
-        <v>0.7149935684156314</v>
+        <v>0.71499356841563144</v>
       </c>
       <c r="D186">
         <v>-499</v>
@@ -5225,18 +4683,15 @@
         <v>2928469922.12919</v>
       </c>
       <c r="F186">
-        <v>-14639445.61954908</v>
+        <v>-785.23319361231802</v>
       </c>
       <c r="G186">
-        <v>134.2328068970648</v>
-      </c>
-      <c r="H186">
-        <v>0.2850064315843686</v>
-      </c>
-    </row>
-    <row r="187" spans="1:8">
+        <v>0.28500643158436861</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A187">
-        <v>16093.1316</v>
+        <v>16093.131600000001</v>
       </c>
       <c r="B187">
         <v>16093.1242</v>
@@ -5248,19 +4703,16 @@
         <v>-771</v>
       </c>
       <c r="E187">
-        <v>5881421966.728233</v>
+        <v>5881421966.7282333</v>
       </c>
       <c r="F187">
-        <v>42492104.45779014</v>
+        <v>2281.01373570442</v>
       </c>
       <c r="G187">
-        <v>-137.8516154967916</v>
-      </c>
-      <c r="H187">
         <v>0.2468524416413167</v>
       </c>
     </row>
-    <row r="188" spans="1:8">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A188">
         <v>16160.9789</v>
       </c>
@@ -5268,137 +4720,122 @@
         <v>16160.9845</v>
       </c>
       <c r="C188">
-        <v>0.7872591390190221</v>
+        <v>0.78725913901902211</v>
       </c>
       <c r="D188">
         <v>-529</v>
       </c>
       <c r="E188">
-        <v>2618658247.111792</v>
+        <v>2618658247.1117921</v>
       </c>
       <c r="F188">
-        <v>19895462.42167929</v>
+        <v>1072.509501947148</v>
       </c>
       <c r="G188">
-        <v>103.8821828568387</v>
-      </c>
-      <c r="H188">
-        <v>0.2127408609809779</v>
-      </c>
-    </row>
-    <row r="189" spans="1:8">
+        <v>0.21274086098097791</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A189">
-        <v>16179.3972</v>
+        <v>16179.397199999999</v>
       </c>
       <c r="B189">
-        <v>16179.4163</v>
+        <v>16179.416300000001</v>
       </c>
       <c r="C189">
-        <v>0.7331805656811385</v>
+        <v>0.73318056568113854</v>
       </c>
       <c r="D189">
         <v>-279</v>
       </c>
       <c r="E189">
-        <v>2829358146.408769</v>
+        <v>2829358146.4087691</v>
       </c>
       <c r="F189">
-        <v>36547100.96472555</v>
+        <v>1972.400389960532</v>
       </c>
       <c r="G189">
-        <v>353.9091028653904</v>
-      </c>
-      <c r="H189">
-        <v>0.2668194343188615</v>
-      </c>
-    </row>
-    <row r="190" spans="1:8">
+        <v>0.26681943431886151</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A190">
-        <v>16185.3311</v>
+        <v>16185.331099999999</v>
       </c>
       <c r="B190">
         <v>16185.349</v>
       </c>
       <c r="C190">
-        <v>0.7089498446341125</v>
+        <v>0.70894984463411248</v>
       </c>
       <c r="D190">
         <v>-301</v>
       </c>
       <c r="E190">
-        <v>3133390673.07931</v>
+        <v>3133390673.0793099</v>
       </c>
       <c r="F190">
-        <v>4532024.68046705</v>
+        <v>244.67727313531239</v>
       </c>
       <c r="G190">
-        <v>331.5523769479758</v>
-      </c>
-      <c r="H190">
-        <v>0.2910501553658875</v>
-      </c>
-    </row>
-    <row r="191" spans="1:8">
+        <v>0.29105015536588752</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A191">
-        <v>16199.487</v>
+        <v>16199.486999999999</v>
       </c>
       <c r="B191">
-        <v>16199.5055</v>
+        <v>16199.505499999999</v>
       </c>
       <c r="C191">
-        <v>0.7366726410096687</v>
+        <v>0.73667264100966867</v>
       </c>
       <c r="D191">
         <v>-291</v>
       </c>
       <c r="E191">
-        <v>2764932351.493311</v>
+        <v>2764932351.4933109</v>
       </c>
       <c r="F191">
-        <v>-16619189.83752748</v>
+        <v>-898.03012048612152</v>
       </c>
       <c r="G191">
-        <v>342.3664263381521</v>
-      </c>
-      <c r="H191">
-        <v>0.2633273589903313</v>
-      </c>
-    </row>
-    <row r="192" spans="1:8">
+        <v>0.26332735899033127</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A192">
-        <v>16202.9307</v>
+        <v>16202.930700000001</v>
       </c>
       <c r="B192">
-        <v>16202.9351</v>
+        <v>16202.935100000001</v>
       </c>
       <c r="C192">
-        <v>0.6616706907977927</v>
+        <v>0.66167069079779273</v>
       </c>
       <c r="D192">
         <v>-552</v>
       </c>
       <c r="E192">
-        <v>4044677549.196068</v>
+        <v>4044677549.1960678</v>
       </c>
       <c r="F192">
-        <v>-15095353.39127744</v>
+        <v>-815.86118924457128</v>
       </c>
       <c r="G192">
-        <v>81.41038431483929</v>
-      </c>
-      <c r="H192">
-        <v>0.3383293092022073</v>
-      </c>
-    </row>
-    <row r="193" spans="1:8">
+        <v>0.33832930920220727</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A193">
-        <v>16208.6822</v>
+        <v>16208.682199999999</v>
       </c>
       <c r="B193">
         <v>16208.6872</v>
       </c>
       <c r="C193">
-        <v>0.7278238862807881</v>
+        <v>0.72782388628078809</v>
       </c>
       <c r="D193">
         <v>-541</v>
@@ -5407,16 +4844,13 @@
         <v>2093577827.286536</v>
       </c>
       <c r="F193">
-        <v>39141542.31144371</v>
+        <v>2116.2407489642592</v>
       </c>
       <c r="G193">
-        <v>92.47897340587421</v>
-      </c>
-      <c r="H193">
-        <v>0.2721761137192119</v>
-      </c>
-    </row>
-    <row r="194" spans="1:8">
+        <v>0.27217611371921191</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A194">
         <v>16212.1746</v>
       </c>
@@ -5424,33 +4858,30 @@
         <v>16212.1958</v>
       </c>
       <c r="C194">
-        <v>0.6534248919502296</v>
+        <v>0.65342489195022957</v>
       </c>
       <c r="D194">
         <v>-241</v>
       </c>
       <c r="E194">
-        <v>3179222056.615446</v>
+        <v>3179222056.6154461</v>
       </c>
       <c r="F194">
-        <v>-28992438.82611369</v>
+        <v>-1567.854969081568</v>
       </c>
       <c r="G194">
-        <v>392.0263793176198</v>
-      </c>
-      <c r="H194">
-        <v>0.3465751080497704</v>
-      </c>
-    </row>
-    <row r="195" spans="1:8">
+        <v>0.34657510804977038</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A195">
-        <v>16230.0565</v>
+        <v>16230.056500000001</v>
       </c>
       <c r="B195">
         <v>16230.0738</v>
       </c>
       <c r="C195">
-        <v>0.7720908522244843</v>
+        <v>0.77209085222448426</v>
       </c>
       <c r="D195">
         <v>-313</v>
@@ -5459,42 +4890,36 @@
         <v>2576563446.582314</v>
       </c>
       <c r="F195">
-        <v>-4456211.232154349</v>
+        <v>-241.24902156896161</v>
       </c>
       <c r="G195">
-        <v>319.5558514401135</v>
-      </c>
-      <c r="H195">
-        <v>0.2279091477755157</v>
-      </c>
-    </row>
-    <row r="196" spans="1:8">
+        <v>0.22790914777551571</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A196">
-        <v>16236.0883</v>
+        <v>16236.088299999999</v>
       </c>
       <c r="B196">
-        <v>16236.1071</v>
+        <v>16236.107099999999</v>
       </c>
       <c r="C196">
-        <v>0.6668825032047929</v>
+        <v>0.66688250320479292</v>
       </c>
       <c r="D196">
         <v>-286</v>
       </c>
       <c r="E196">
-        <v>3095424452.912705</v>
+        <v>3095424452.9127049</v>
       </c>
       <c r="F196">
-        <v>-15887395.34195823</v>
+        <v>-860.42675667336141</v>
       </c>
       <c r="G196">
-        <v>347.1339959839592</v>
-      </c>
-      <c r="H196">
-        <v>0.3331174967952071</v>
-      </c>
-    </row>
-    <row r="197" spans="1:8">
+        <v>0.33311749679520708</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A197">
         <v>16240.4048</v>
       </c>
@@ -5502,7 +4927,7 @@
         <v>16240.4167</v>
       </c>
       <c r="C197">
-        <v>0.7590633069537319</v>
+        <v>0.75906330695373192</v>
       </c>
       <c r="D197">
         <v>-413</v>
@@ -5511,42 +4936,36 @@
         <v>2524462559.141798</v>
       </c>
       <c r="F197">
-        <v>20463206.05191058</v>
+        <v>1108.536870867478</v>
       </c>
       <c r="G197">
-        <v>219.6700325181319</v>
-      </c>
-      <c r="H197">
-        <v>0.2409366930462681</v>
-      </c>
-    </row>
-    <row r="198" spans="1:8">
+        <v>0.24093669304626811</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A198">
-        <v>16250.9009</v>
+        <v>16250.900900000001</v>
       </c>
       <c r="B198">
-        <v>16250.9155</v>
+        <v>16250.915499999999</v>
       </c>
       <c r="C198">
-        <v>0.8028817560778079</v>
+        <v>0.80288175607780787</v>
       </c>
       <c r="D198">
         <v>-364</v>
       </c>
       <c r="E198">
-        <v>2387424251.933375</v>
+        <v>2387424251.9333749</v>
       </c>
       <c r="F198">
-        <v>21318329.71836824</v>
+        <v>1155.6073730658729</v>
       </c>
       <c r="G198">
-        <v>269.3370609356932</v>
-      </c>
-      <c r="H198">
         <v>0.1971182439221921</v>
       </c>
     </row>
-    <row r="199" spans="1:8">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A199">
         <v>16289.221</v>
       </c>
@@ -5554,27 +4973,24 @@
         <v>16289.2444</v>
       </c>
       <c r="C199">
-        <v>0.7578182065394375</v>
+        <v>0.75781820653943754</v>
       </c>
       <c r="D199">
         <v>-202</v>
       </c>
       <c r="E199">
-        <v>2701662462.370373</v>
+        <v>2701662462.3703728</v>
       </c>
       <c r="F199">
-        <v>22456878.06023574</v>
+        <v>1220.1960570474989</v>
       </c>
       <c r="G199">
-        <v>430.6616944641905</v>
-      </c>
-      <c r="H199">
-        <v>0.2421817934605625</v>
-      </c>
-    </row>
-    <row r="200" spans="1:8">
+        <v>0.24218179346056251</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A200">
-        <v>16297.2992</v>
+        <v>16297.299199999999</v>
       </c>
       <c r="B200">
         <v>16297.3014</v>
@@ -5586,45 +5002,39 @@
         <v>-593</v>
       </c>
       <c r="E200">
-        <v>2373912766.56643</v>
+        <v>2373912766.5664301</v>
       </c>
       <c r="F200">
-        <v>6287354.073957154</v>
+        <v>341.79280237862957</v>
       </c>
       <c r="G200">
-        <v>40.46949130141842</v>
-      </c>
-      <c r="H200">
         <v>0.193477939367108</v>
       </c>
     </row>
-    <row r="201" spans="1:8">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A201">
-        <v>16320.783</v>
+        <v>16320.782999999999</v>
       </c>
       <c r="B201">
         <v>16320.81</v>
       </c>
       <c r="C201">
-        <v>0.5589444414247435</v>
+        <v>0.55894444142474353</v>
       </c>
       <c r="D201">
         <v>-137</v>
       </c>
       <c r="E201">
-        <v>2288132164.547809</v>
+        <v>2288132164.5478091</v>
       </c>
       <c r="F201">
-        <v>51227219.09015395</v>
+        <v>2788.8283620489719</v>
       </c>
       <c r="G201">
-        <v>495.9563745355763</v>
-      </c>
-      <c r="H201">
-        <v>0.4410555585752565</v>
-      </c>
-    </row>
-    <row r="202" spans="1:8">
+        <v>0.44105555857525652</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A202">
         <v>16323.1594</v>
       </c>
@@ -5638,19 +5048,16 @@
         <v>-442</v>
       </c>
       <c r="E202">
-        <v>2344624347.877722</v>
+        <v>2344624347.8777218</v>
       </c>
       <c r="F202">
-        <v>3006011.11654563</v>
+        <v>163.671995631264</v>
       </c>
       <c r="G202">
-        <v>191.0072361620598</v>
-      </c>
-      <c r="H202">
         <v>0.203581244422123</v>
       </c>
     </row>
-    <row r="203" spans="1:8">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A203">
         <v>16335.9908</v>
       </c>
@@ -5658,25 +5065,22 @@
         <v>16335.9928</v>
       </c>
       <c r="C203">
-        <v>0.8181297780099491</v>
+        <v>0.81812977800994913</v>
       </c>
       <c r="D203">
         <v>-596</v>
       </c>
       <c r="E203">
-        <v>2324035744.369361</v>
+        <v>2324035744.3693609</v>
       </c>
       <c r="F203">
-        <v>-39089639.85088311</v>
+        <v>-2130.0338221271049</v>
       </c>
       <c r="G203">
-        <v>36.7033088949083</v>
-      </c>
-      <c r="H203">
         <v>0.1818702219900509</v>
       </c>
     </row>
-    <row r="204" spans="1:8">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A204">
         <v>16388.6201</v>
       </c>
@@ -5684,7 +5088,7 @@
         <v>16388.6315</v>
       </c>
       <c r="C204">
-        <v>0.8419927791338409</v>
+        <v>0.84199277913384085</v>
       </c>
       <c r="D204">
         <v>-424</v>
@@ -5693,73 +5097,64 @@
         <v>1935730441.132565</v>
       </c>
       <c r="F204">
-        <v>120891807.0093691</v>
+        <v>6608.7428938778276</v>
       </c>
       <c r="G204">
-        <v>208.5370214600775</v>
-      </c>
-      <c r="H204">
-        <v>0.1580072208661591</v>
-      </c>
-    </row>
-    <row r="205" spans="1:8">
+        <v>0.15800722086615909</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A205">
         <v>16398.8704</v>
       </c>
       <c r="B205">
-        <v>16398.8782</v>
+        <v>16398.878199999999</v>
       </c>
       <c r="C205">
-        <v>0.6466939110352631</v>
+        <v>0.64669391103526308</v>
       </c>
       <c r="D205">
         <v>-490</v>
       </c>
       <c r="E205">
-        <v>3128094910.877211</v>
+        <v>3128094910.8772111</v>
       </c>
       <c r="F205">
-        <v>-12752656.47561182</v>
+        <v>-697.58012481421213</v>
       </c>
       <c r="G205">
-        <v>142.5940394123858</v>
-      </c>
-      <c r="H205">
-        <v>0.3533060889647369</v>
-      </c>
-    </row>
-    <row r="206" spans="1:8">
+        <v>0.35330608896473692</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A206">
-        <v>16409.0824</v>
+        <v>16409.082399999999</v>
       </c>
       <c r="B206">
-        <v>16409.1</v>
+        <v>16409.099999999999</v>
       </c>
       <c r="C206">
-        <v>0.6814376280678456</v>
+        <v>0.68143762806784558</v>
       </c>
       <c r="D206">
         <v>-311</v>
       </c>
       <c r="E206">
-        <v>2985467084.742025</v>
+        <v>2985467084.7420249</v>
       </c>
       <c r="F206">
-        <v>-7865713.081280822</v>
+        <v>-430.52875106699679</v>
       </c>
       <c r="G206">
-        <v>321.5504153084832</v>
-      </c>
-      <c r="H206">
-        <v>0.3185623719321544</v>
-      </c>
-    </row>
-    <row r="207" spans="1:8">
+        <v>0.31856237193215442</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A207">
         <v>16441.1165</v>
       </c>
       <c r="B207">
-        <v>16441.1238</v>
+        <v>16441.123800000001</v>
       </c>
       <c r="C207">
         <v>0.7732216211460432</v>
@@ -5768,27 +5163,24 @@
         <v>-500</v>
       </c>
       <c r="E207">
-        <v>2539554703.956648</v>
+        <v>2539554703.9566479</v>
       </c>
       <c r="F207">
-        <v>-28550976.2097047</v>
+        <v>-1565.783667828661</v>
       </c>
       <c r="G207">
-        <v>133.1104821214017</v>
-      </c>
-      <c r="H207">
         <v>0.2267783788539568</v>
       </c>
     </row>
-    <row r="208" spans="1:8">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A208">
-        <v>16444.8936</v>
+        <v>16444.893599999999</v>
       </c>
       <c r="B208">
-        <v>16444.9108</v>
+        <v>16444.910800000001</v>
       </c>
       <c r="C208">
-        <v>0.8159661726074854</v>
+        <v>0.81596617260748538</v>
       </c>
       <c r="D208">
         <v>-319</v>
@@ -5797,203 +5189,179 @@
         <v>2122137809.853559</v>
       </c>
       <c r="F208">
-        <v>65936362.86466946</v>
+        <v>3616.894210814075</v>
       </c>
       <c r="G208">
-        <v>313.5581417605769</v>
-      </c>
-      <c r="H208">
-        <v>0.1840338273925146</v>
-      </c>
-    </row>
-    <row r="209" spans="1:8">
+        <v>0.18403382739251459</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A209">
-        <v>16449.311</v>
+        <v>16449.311000000002</v>
       </c>
       <c r="B209">
-        <v>16449.332</v>
+        <v>16449.331999999999</v>
       </c>
       <c r="C209">
-        <v>0.5725433337183199</v>
+        <v>0.57254333371831989</v>
       </c>
       <c r="D209">
         <v>-250</v>
       </c>
       <c r="E209">
-        <v>3267782809.83175</v>
+        <v>3267782809.8317499</v>
       </c>
       <c r="F209">
-        <v>-32685213.94314819</v>
+        <v>-1793.407143157262</v>
       </c>
       <c r="G209">
-        <v>382.7298065708976</v>
-      </c>
-      <c r="H209">
-        <v>0.4274566662816801</v>
-      </c>
-    </row>
-    <row r="210" spans="1:8">
+        <v>0.42745666628168011</v>
+      </c>
+    </row>
+    <row r="210" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A210">
         <v>16491.1731</v>
       </c>
       <c r="B210">
-        <v>16491.1968</v>
+        <v>16491.196800000002</v>
       </c>
       <c r="C210">
-        <v>0.548082591536858</v>
+        <v>0.54808259153685801</v>
       </c>
       <c r="D210">
         <v>-202</v>
       </c>
       <c r="E210">
-        <v>2910109884.384812</v>
+        <v>2910109884.3848119</v>
       </c>
       <c r="F210">
-        <v>-11321095.68117637</v>
+        <v>-622.75888498138818</v>
       </c>
       <c r="G210">
-        <v>430.8414697035229</v>
-      </c>
-      <c r="H210">
-        <v>0.451917408463142</v>
-      </c>
-    </row>
-    <row r="211" spans="1:8">
+        <v>0.45191740846314199</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A211">
-        <v>16521.7407</v>
+        <v>16521.740699999998</v>
       </c>
       <c r="B211">
-        <v>16521.7615</v>
+        <v>16521.761500000001</v>
       </c>
       <c r="C211">
-        <v>0.6355173365191923</v>
+        <v>0.63551733651919229</v>
       </c>
       <c r="D211">
         <v>-256</v>
       </c>
       <c r="E211">
-        <v>3265067322.629371</v>
+        <v>3265067322.6293712</v>
       </c>
       <c r="F211">
-        <v>2226455.036940136</v>
+        <v>122.70141602694559</v>
       </c>
       <c r="G211">
-        <v>377.4228902383945</v>
-      </c>
-      <c r="H211">
-        <v>0.3644826634808077</v>
-      </c>
-    </row>
-    <row r="212" spans="1:8">
+        <v>0.36448266348080771</v>
+      </c>
+    </row>
+    <row r="212" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A212">
-        <v>16543.7138</v>
+        <v>16543.713800000001</v>
       </c>
       <c r="B212">
-        <v>16543.7318</v>
+        <v>16543.731800000001</v>
       </c>
       <c r="C212">
-        <v>0.8119569201038782</v>
+        <v>0.81195692010387821</v>
       </c>
       <c r="D212">
         <v>-307</v>
       </c>
       <c r="E212">
-        <v>2365213727.85796</v>
+        <v>2365213727.8579602</v>
       </c>
       <c r="F212">
-        <v>-30673859.85569298</v>
+        <v>-1692.704726825955</v>
       </c>
       <c r="G212">
-        <v>326.1821565130869</v>
-      </c>
-      <c r="H212">
-        <v>0.1880430798961218</v>
-      </c>
-    </row>
-    <row r="213" spans="1:8">
+        <v>0.18804307989612179</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A213">
-        <v>16556.5189</v>
+        <v>16556.518899999999</v>
       </c>
       <c r="B213">
-        <v>16556.5413</v>
+        <v>16556.541300000001</v>
       </c>
       <c r="C213">
-        <v>0.7755126102414642</v>
+        <v>0.77551261024146423</v>
       </c>
       <c r="D213">
         <v>-227</v>
       </c>
       <c r="E213">
-        <v>2429909011.294053</v>
+        <v>2429909011.2940531</v>
       </c>
       <c r="F213">
-        <v>16523722.63063598</v>
+        <v>912.55029559105617</v>
       </c>
       <c r="G213">
-        <v>405.6016304391342</v>
-      </c>
-      <c r="H213">
         <v>0.2244873897585358</v>
       </c>
     </row>
-    <row r="214" spans="1:8">
+    <row r="214" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A214">
-        <v>16566.2943</v>
+        <v>16566.294300000001</v>
       </c>
       <c r="B214">
-        <v>16566.3244</v>
+        <v>16566.324400000001</v>
       </c>
       <c r="C214">
-        <v>0.6629796087065615</v>
+        <v>0.66297960870656147</v>
       </c>
       <c r="D214">
         <v>-88</v>
       </c>
       <c r="E214">
-        <v>3024902844.993293</v>
+        <v>3024902844.9932928</v>
       </c>
       <c r="F214">
-        <v>-26526815.54057986</v>
+        <v>-1465.8535257221431</v>
       </c>
       <c r="G214">
-        <v>544.7055824357349</v>
-      </c>
-      <c r="H214">
-        <v>0.3370203912934385</v>
-      </c>
-    </row>
-    <row r="215" spans="1:8">
+        <v>0.33702039129343853</v>
+      </c>
+    </row>
+    <row r="215" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A215">
-        <v>16650.4242</v>
+        <v>16650.424200000001</v>
       </c>
       <c r="B215">
-        <v>16650.4281</v>
+        <v>16650.428100000001</v>
       </c>
       <c r="C215">
-        <v>0.7359833921838086</v>
+        <v>0.73598339218380859</v>
       </c>
       <c r="D215">
         <v>-563</v>
       </c>
       <c r="E215">
-        <v>2935604332.999224</v>
+        <v>2935604332.9992242</v>
       </c>
       <c r="F215">
-        <v>9043179.713305684</v>
+        <v>502.25684333851677</v>
       </c>
       <c r="G215">
-        <v>70.21986776515132</v>
-      </c>
-      <c r="H215">
-        <v>0.2640166078161914</v>
-      </c>
-    </row>
-    <row r="216" spans="1:8">
+        <v>0.26401660781619141</v>
+      </c>
+    </row>
+    <row r="216" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A216">
-        <v>16670.0368</v>
+        <v>16670.036800000002</v>
       </c>
       <c r="B216">
-        <v>16670.0434</v>
+        <v>16670.043399999999</v>
       </c>
       <c r="C216">
         <v>0.7394622399229378</v>
@@ -6005,47 +5373,41 @@
         <v>2969276017.595953</v>
       </c>
       <c r="F216">
-        <v>-45951324.73962834</v>
+        <v>-2555.136252617463</v>
       </c>
       <c r="G216">
-        <v>118.6938124995394</v>
-      </c>
-      <c r="H216">
         <v>0.2605377600770622</v>
       </c>
     </row>
-    <row r="217" spans="1:8">
+    <row r="217" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A217">
         <v>16727.8488</v>
       </c>
       <c r="B217">
-        <v>16727.8538</v>
+        <v>16727.853800000001</v>
       </c>
       <c r="C217">
-        <v>0.775821846023496</v>
+        <v>0.77582184602349602</v>
       </c>
       <c r="D217">
         <v>-543</v>
       </c>
       <c r="E217">
-        <v>2397325331.73465</v>
+        <v>2397325331.7346501</v>
       </c>
       <c r="F217">
-        <v>35583227.94198732</v>
+        <v>1985.4770153878881</v>
       </c>
       <c r="G217">
-        <v>89.6087900242761</v>
-      </c>
-      <c r="H217">
-        <v>0.224178153976504</v>
-      </c>
-    </row>
-    <row r="218" spans="1:8">
+        <v>0.22417815397650401</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A218">
         <v>16730.0121</v>
       </c>
       <c r="B218">
-        <v>16730.0185</v>
+        <v>16730.018499999998</v>
       </c>
       <c r="C218">
         <v>0.9487484707746483</v>
@@ -6054,79 +5416,70 @@
         <v>-518</v>
       </c>
       <c r="E218">
-        <v>505954929.6191821</v>
+        <v>505954929.61918211</v>
       </c>
       <c r="F218">
-        <v>315653138.2201879</v>
+        <v>17615.129070414441</v>
       </c>
       <c r="G218">
-        <v>114.684419813436</v>
-      </c>
-      <c r="H218">
-        <v>0.0512515292253517</v>
-      </c>
-    </row>
-    <row r="219" spans="1:8">
+        <v>5.12515292253517E-2</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A219">
-        <v>16757.6467</v>
+        <v>16757.646700000001</v>
       </c>
       <c r="B219">
-        <v>16757.6644</v>
+        <v>16757.664400000001</v>
       </c>
       <c r="C219">
-        <v>0.7456992725513314</v>
+        <v>0.74569927255133139</v>
       </c>
       <c r="D219">
         <v>-316</v>
       </c>
       <c r="E219">
-        <v>2634097295.423865</v>
+        <v>2634097295.4238648</v>
       </c>
       <c r="F219">
-        <v>-14186611.91552306</v>
+        <v>-792.99687203397446</v>
       </c>
       <c r="G219">
-        <v>316.651054994061</v>
-      </c>
-      <c r="H219">
-        <v>0.2543007274486686</v>
-      </c>
-    </row>
-    <row r="220" spans="1:8">
+        <v>0.25430072744866861</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A220">
         <v>16804.2402</v>
       </c>
       <c r="B220">
-        <v>16804.247</v>
+        <v>16804.246999999999</v>
       </c>
       <c r="C220">
-        <v>0.7977392547178709</v>
+        <v>0.79773925471787088</v>
       </c>
       <c r="D220">
         <v>-512</v>
       </c>
       <c r="E220">
-        <v>2153922306.858066</v>
+        <v>2153922306.8580661</v>
       </c>
       <c r="F220">
-        <v>104028839.900463</v>
+        <v>5831.1217449334081</v>
       </c>
       <c r="G220">
-        <v>121.3139475424352</v>
-      </c>
-      <c r="H220">
-        <v>0.2022607452821291</v>
-      </c>
-    </row>
-    <row r="221" spans="1:8">
+        <v>0.20226074528212909</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A221">
-        <v>16974.5482</v>
+        <v>16974.548200000001</v>
       </c>
       <c r="B221">
-        <v>16974.5567</v>
+        <v>16974.556700000001</v>
       </c>
       <c r="C221">
-        <v>0.724950353792886</v>
+        <v>0.72495035379288597</v>
       </c>
       <c r="D221">
         <v>-483</v>
@@ -6135,50 +5488,44 @@
         <v>2738149516.287169</v>
       </c>
       <c r="F221">
-        <v>5315605.952762325</v>
+        <v>300.97506535678627</v>
       </c>
       <c r="G221">
-        <v>150.1209848485497</v>
-      </c>
-      <c r="H221">
-        <v>0.275049646207114</v>
-      </c>
-    </row>
-    <row r="222" spans="1:8">
+        <v>0.27504964620711397</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A222">
-        <v>17015.7476</v>
+        <v>17015.747599999999</v>
       </c>
       <c r="B222">
         <v>17015.7533</v>
       </c>
       <c r="C222">
-        <v>0.7088815066111245</v>
+        <v>0.70888150661112448</v>
       </c>
       <c r="D222">
         <v>-533</v>
       </c>
       <c r="E222">
-        <v>3196825565.453818</v>
+        <v>3196825565.4538178</v>
       </c>
       <c r="F222">
-        <v>-39561255.61846042</v>
+        <v>-2245.4352932453071</v>
       </c>
       <c r="G222">
-        <v>100.4256205295912</v>
-      </c>
-      <c r="H222">
-        <v>0.2911184933888755</v>
-      </c>
-    </row>
-    <row r="223" spans="1:8">
+        <v>0.29111849338887552</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A223">
-        <v>17042.4469</v>
+        <v>17042.446899999999</v>
       </c>
       <c r="B223">
         <v>17042.45</v>
       </c>
       <c r="C223">
-        <v>0.8692643355683184</v>
+        <v>0.86926433556831839</v>
       </c>
       <c r="D223">
         <v>-578</v>
@@ -6187,24 +5534,21 @@
         <v>1499806598.330992</v>
       </c>
       <c r="F223">
-        <v>-27980409.52283004</v>
+        <v>-1590.616166442569</v>
       </c>
       <c r="G223">
-        <v>54.53187711609101</v>
-      </c>
-      <c r="H223">
-        <v>0.1307356644316816</v>
-      </c>
-    </row>
-    <row r="224" spans="1:8">
+        <v>0.13073566443168161</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A224">
         <v>17165.7965</v>
       </c>
       <c r="B224">
-        <v>17165.8042</v>
+        <v>17165.804199999999</v>
       </c>
       <c r="C224">
-        <v>0.751672813992473</v>
+        <v>0.75167281399247299</v>
       </c>
       <c r="D224">
         <v>-499</v>
@@ -6213,117 +5557,102 @@
         <v>2868653579.087183</v>
       </c>
       <c r="F224">
-        <v>-9407379.650744831</v>
+        <v>-538.65677007708496</v>
       </c>
       <c r="G224">
-        <v>134.4768316275478</v>
-      </c>
-      <c r="H224">
-        <v>0.248327186007527</v>
-      </c>
-    </row>
-    <row r="225" spans="1:8">
+        <v>0.24832718600752701</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A225">
         <v>17209.0026</v>
       </c>
       <c r="B225">
-        <v>17209.0074</v>
+        <v>17209.007399999999</v>
       </c>
       <c r="C225">
-        <v>0.7264891303280261</v>
+        <v>0.72648913032802609</v>
       </c>
       <c r="D225">
         <v>-549</v>
       </c>
       <c r="E225">
-        <v>2297603256.137409</v>
+        <v>2297603256.1374092</v>
       </c>
       <c r="F225">
-        <v>-55151778.96647949</v>
+        <v>-3165.8814190626158</v>
       </c>
       <c r="G225">
-        <v>83.61924462412458</v>
-      </c>
-      <c r="H225">
-        <v>0.2735108696719739</v>
-      </c>
-    </row>
-    <row r="226" spans="1:8">
+        <v>0.27351086967197391</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A226">
-        <v>17307.0446</v>
+        <v>17307.044600000001</v>
       </c>
       <c r="B226">
         <v>17307.05</v>
       </c>
       <c r="C226">
-        <v>0.7003135674604529</v>
+        <v>0.70031356746045292</v>
       </c>
       <c r="D226">
         <v>-539</v>
       </c>
       <c r="E226">
-        <v>3115670104.780177</v>
+        <v>3115670104.7801771</v>
       </c>
       <c r="F226">
-        <v>20684258.06144327</v>
+        <v>1194.10438431477</v>
       </c>
       <c r="G226">
-        <v>93.53874735469434</v>
-      </c>
-      <c r="H226">
-        <v>0.2996864325395471</v>
-      </c>
-    </row>
-    <row r="227" spans="1:8">
+        <v>0.29968643253954708</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A227">
-        <v>17315.5826</v>
+        <v>17315.582600000002</v>
       </c>
       <c r="B227">
-        <v>17315.5846</v>
+        <v>17315.584599999998</v>
       </c>
       <c r="C227">
-        <v>0.9281820059124292</v>
+        <v>0.92818200591242916</v>
       </c>
       <c r="D227">
         <v>-598</v>
       </c>
       <c r="E227">
-        <v>2184124492.427251</v>
+        <v>2184124492.4272509</v>
       </c>
       <c r="F227">
-        <v>-59042938.8992428</v>
+        <v>-3410.2359024070902</v>
       </c>
       <c r="G227">
-        <v>34.6268981373526</v>
-      </c>
-      <c r="H227">
-        <v>0.07181799408757084</v>
-      </c>
-    </row>
-    <row r="228" spans="1:8">
+        <v>7.1817994087570836E-2</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A228">
-        <v>17688.7397</v>
+        <v>17688.739699999998</v>
       </c>
       <c r="B228">
-        <v>17688.7463</v>
+        <v>17688.746299999999</v>
       </c>
       <c r="C228">
-        <v>0.7287877848095923</v>
+        <v>0.72878778480959228</v>
       </c>
       <c r="D228">
         <v>-521</v>
       </c>
       <c r="E228">
-        <v>2313138605.45255</v>
+        <v>2313138605.4525499</v>
       </c>
       <c r="F228">
-        <v>-12747770.98337865</v>
+        <v>-752.16063912950847</v>
       </c>
       <c r="G228">
-        <v>111.8581796353327</v>
-      </c>
-      <c r="H228">
-        <v>0.2712122151904077</v>
+        <v>0.27121221519040772</v>
       </c>
     </row>
   </sheetData>
